--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E747D59E-9DE4-4636-9217-84437E6A1BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92504562-4A67-427E-9375-CFBD07B83708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-720" yWindow="10940" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="380" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -491,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -530,9 +530,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -888,7 +885,7 @@
       <c r="H2" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="15" t="s">
         <v>84</v>
       </c>
     </row>
@@ -911,7 +908,7 @@
       <c r="F3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -922,6 +919,9 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>10001</v>
+      </c>
       <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
@@ -938,11 +938,14 @@
       <c r="H4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="14" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>10001</v>
+      </c>
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
@@ -962,6 +965,9 @@
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>10001</v>
+      </c>
       <c r="C6" s="7" t="s">
         <v>11</v>
       </c>
@@ -981,6 +987,9 @@
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>10001</v>
+      </c>
       <c r="C7" s="7" t="s">
         <v>12</v>
       </c>
@@ -1000,6 +1009,9 @@
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>10001</v>
+      </c>
       <c r="C8" s="7" t="s">
         <v>13</v>
       </c>
@@ -1016,11 +1028,14 @@
       <c r="H8" s="4">
         <v>1</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="14" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>10001</v>
+      </c>
       <c r="C9" s="7" t="s">
         <v>14</v>
       </c>
@@ -1040,6 +1055,9 @@
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>10001</v>
+      </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
       </c>
@@ -1059,6 +1077,9 @@
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>10001</v>
+      </c>
       <c r="C11" s="7" t="s">
         <v>16</v>
       </c>
@@ -1078,6 +1099,9 @@
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>10001</v>
+      </c>
       <c r="C12" s="7" t="s">
         <v>17</v>
       </c>
@@ -1097,6 +1121,9 @@
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>10001</v>
+      </c>
       <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
@@ -1113,11 +1140,14 @@
       <c r="H13" s="4">
         <v>1</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="14">
         <v>100010</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>10001</v>
+      </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
@@ -1137,6 +1167,9 @@
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>10001</v>
+      </c>
       <c r="C15" s="7" t="s">
         <v>20</v>
       </c>
@@ -1156,6 +1189,9 @@
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <v>10001</v>
+      </c>
       <c r="C16" s="7" t="s">
         <v>21</v>
       </c>
@@ -1174,7 +1210,10 @@
       </c>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
+        <v>10001</v>
+      </c>
       <c r="C17" s="7" t="s">
         <v>22</v>
       </c>
@@ -1193,7 +1232,10 @@
       </c>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
+        <v>10001</v>
+      </c>
       <c r="C18" s="7" t="s">
         <v>23</v>
       </c>
@@ -1212,7 +1254,10 @@
       </c>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
+        <v>10001</v>
+      </c>
       <c r="C19" s="7" t="s">
         <v>24</v>
       </c>
@@ -1231,7 +1276,10 @@
       </c>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
+        <v>10001</v>
+      </c>
       <c r="C20" s="7" t="s">
         <v>25</v>
       </c>
@@ -1250,7 +1298,10 @@
       </c>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
+        <v>10001</v>
+      </c>
       <c r="C21" s="7" t="s">
         <v>26</v>
       </c>
@@ -1269,7 +1320,10 @@
       </c>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="1">
+        <v>10001</v>
+      </c>
       <c r="C22" s="7" t="s">
         <v>27</v>
       </c>
@@ -1288,7 +1342,10 @@
       </c>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="1">
+        <v>10001</v>
+      </c>
       <c r="C23" s="8" t="s">
         <v>28</v>
       </c>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92504562-4A67-427E-9375-CFBD07B83708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F070CA0C-293F-44F5-AC4A-8A951C417C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="380" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="131">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -228,63 +228,6 @@
     <t>SceneImage</t>
   </si>
   <si>
-    <t>SceneApartmentLivingRoomKitchen</t>
-  </si>
-  <si>
-    <t>SceneTheHeroinesRoom</t>
-  </si>
-  <si>
-    <t>SceneTheMaleProtagonistsRoom</t>
-  </si>
-  <si>
-    <t>SceneBathroom</t>
-  </si>
-  <si>
-    <t>SceneCommercialStreet</t>
-  </si>
-  <si>
-    <t>SceneSupermarket</t>
-  </si>
-  <si>
-    <t>SceneClothShop</t>
-  </si>
-  <si>
-    <t>SceneFreshVegetableShop</t>
-  </si>
-  <si>
-    <t>SceneSexToyStore</t>
-  </si>
-  <si>
-    <t>ScenePark</t>
-  </si>
-  <si>
-    <t>SceneSmallRiver</t>
-  </si>
-  <si>
-    <t>SceneBar</t>
-  </si>
-  <si>
-    <t>SceneCasino</t>
-  </si>
-  <si>
-    <t>SceneSurroundingFactories</t>
-  </si>
-  <si>
-    <t>SceneStudio</t>
-  </si>
-  <si>
-    <t>SceneOutsideTheVenue</t>
-  </si>
-  <si>
-    <t>SceneInsideTheVenue</t>
-  </si>
-  <si>
-    <t>SceneLuxuryApartment</t>
-  </si>
-  <si>
-    <t>SceneCafe</t>
-  </si>
-  <si>
     <t>场景图片</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -292,9 +235,6 @@
     <t>PermanentScene</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>常驻场景</t>
   </si>
   <si>
@@ -304,13 +244,278 @@
     <t>子场景</t>
   </si>
   <si>
-    <t>100001+100002+100003+100018</t>
-  </si>
-  <si>
-    <t>100005+100006+100007+100008</t>
-  </si>
-  <si>
     <t>(list#sep=+),long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界地图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+WordScene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScenePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景路径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneApartmentLivingRoomKitchenName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneTheHeroinesRoomName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneTheMaleProtagonistsRoomName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneBathroomName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneCommercialStreetName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSupermarketName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneClothShopName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneFreshVegetableShopName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSexToyStoreName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneParkName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSmallRiverName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneBarName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneCasinoName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneStudioName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneOutsideTheVenueName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneInsideTheVenueName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneLuxuryApartmentName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneCafeName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneApartmentLivingRoomKitchenDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneTheHeroinesRoomDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneTheMaleProtagonistsRoomDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneBathroomDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneCommercialStreetDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneSupermarketDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneClothShopDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneFreshVegetableShopDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneSexToyStoreDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneParkDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneSmallRiverDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneBarDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneCasinoDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneSurroundingFactoriesDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneStudioDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneOutsideTheVenueDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneInsideTheVenueDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneLuxuryApartmentDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+SceneCafeDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene+WordSceneDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PermanentSceneType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常驻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSurroundingFactoriesName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001+10002+10003+10018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10005+10006+10007+10008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordScene</t>
+  </si>
+  <si>
+    <t>SceneApartmentLivingRoomKitchenTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneTheHeroinesRoomTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneTheMaleProtagonistsRoomTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneBathroomTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneCommercialStreetTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSupermarketTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneClothShopTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneFreshVegetableShopTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSexToyStoreTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneParkTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSmallRiverTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneBarTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneCasinoTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSurroundingFactoriesTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneStudioTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneOutsideTheVenueTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneInsideTheVenueTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneLuxuryApartmentTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneCafeTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordSceneTexture</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -374,15 +579,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -487,18 +698,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F2329"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F2329"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -537,6 +756,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -818,554 +1052,692 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="44" style="13" customWidth="1"/>
+    <col min="4" max="4" width="44" style="12" customWidth="1"/>
     <col min="5" max="5" width="44.58203125" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="16.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="29" customWidth="1"/>
+    <col min="6" max="6" width="96.83203125" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="16.58203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I2" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="2">
+      <c r="E4" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="3">
         <v>999999</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="14" t="s">
+      <c r="H4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="3">
+        <v>100000</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="3">
+        <v>100000</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>10004</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3">
+        <v>100000</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>10005</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="3">
+        <v>999999</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>10006</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="3">
+        <v>100004</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>10007</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="3">
+        <v>100004</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>10008</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="3">
+        <v>100004</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>10009</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="3">
+        <v>100004</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>10010</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="3">
+        <v>999999</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J13" s="13">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>10011</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="3">
+        <v>100009</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>10012</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="3">
+        <v>999999</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="3">
+        <v>100011</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
+        <v>10014</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="3">
+        <v>999999</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
+        <v>10015</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="3">
+        <v>100013</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
+        <v>10016</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="3">
+        <v>999999</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
+        <v>10017</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="G20" s="3">
+        <v>100015</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
+        <v>10018</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="3">
+        <v>999999</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="1">
+        <v>10019</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="3">
+        <v>999999</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="1">
+        <v>10020</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="2">
+      <c r="E23" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="3">
         <v>100000</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="2">
-        <v>100000</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="2">
-        <v>100000</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="2">
-        <v>999999</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="2">
-        <v>100004</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="2">
-        <v>100004</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="H23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="1">
+        <v>99999</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="2">
-        <v>100004</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="D24" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="2">
-        <v>100004</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="2">
-        <v>999999</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="14">
-        <v>100010</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="2">
-        <v>100009</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="2">
-        <v>999999</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H15" s="4">
-        <v>1</v>
-      </c>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="2">
-        <v>100011</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H16" s="4">
-        <v>1</v>
-      </c>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="2">
-        <v>999999</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="4">
-        <v>1</v>
-      </c>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="2">
-        <v>100013</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="4">
-        <v>1</v>
-      </c>
-      <c r="I18" s="5"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="2">
-        <v>999999</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="4">
-        <v>1</v>
-      </c>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="2">
-        <v>100015</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" s="4">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="2">
-        <v>999999</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H21" s="4">
-        <v>1</v>
-      </c>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="2">
-        <v>999999</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" s="4">
-        <v>1</v>
-      </c>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="2">
-        <v>100000</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="4">
-        <v>1</v>
-      </c>
-      <c r="I23" s="5"/>
+      <c r="E24" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="16">
+        <v>-1</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J24" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F070CA0C-293F-44F5-AC4A-8A951C417C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E847F15-AB9A-469D-A2E1-AF41CD9BB3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="2890" windowWidth="40970" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="126">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -238,16 +238,6 @@
     <t>常驻场景</t>
   </si>
   <si>
-    <t>SubScene</t>
-  </si>
-  <si>
-    <t>子场景</t>
-  </si>
-  <si>
-    <t>(list#sep=+),long</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>世界地图</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -425,14 +415,6 @@
   </si>
   <si>
     <t>SceneSurroundingFactoriesName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001+10002+10003+10018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10005+10006+10007+10008</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -523,7 +505,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -570,14 +552,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -593,7 +567,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -613,21 +587,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF1F2329"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDEE0E3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -713,7 +672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -727,40 +686,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1052,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
@@ -1063,10 +1016,9 @@
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="16.58203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1083,7 +1035,7 @@
         <v>52</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>54</v>
@@ -1094,11 +1046,8 @@
       <c r="I1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1114,7 +1063,7 @@
       <c r="E2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -1123,14 +1072,11 @@
       <c r="H2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I2" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1147,7 +1093,7 @@
         <v>53</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>55</v>
@@ -1158,11 +1104,8 @@
       <c r="I3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -1172,26 +1115,23 @@
       <c r="D4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>67</v>
+      <c r="E4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="G4" s="3">
         <v>999999</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I4" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I4" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -1201,24 +1141,23 @@
       <c r="D5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>68</v>
+      <c r="E5" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="G5" s="3">
         <v>100000</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -1228,24 +1167,23 @@
       <c r="D6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>69</v>
+      <c r="E6" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="G6" s="3">
         <v>100000</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -1255,24 +1193,23 @@
       <c r="D7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>70</v>
+      <c r="E7" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="G7" s="3">
         <v>100000</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
@@ -1282,26 +1219,23 @@
       <c r="D8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>71</v>
+      <c r="E8" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="G8" s="3">
         <v>999999</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
@@ -1311,24 +1245,23 @@
       <c r="D9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>72</v>
+      <c r="E9" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="G9" s="3">
         <v>100004</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
@@ -1338,24 +1271,23 @@
       <c r="D10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>73</v>
+      <c r="E10" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="G10" s="3">
         <v>100004</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
@@ -1365,24 +1297,23 @@
       <c r="D11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>74</v>
+      <c r="E11" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="G11" s="3">
         <v>100004</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
@@ -1392,24 +1323,23 @@
       <c r="D12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>75</v>
+      <c r="E12" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="G12" s="3">
         <v>100004</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>10010</v>
       </c>
@@ -1419,26 +1349,23 @@
       <c r="D13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>76</v>
+      <c r="E13" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="G13" s="3">
         <v>999999</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="13">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>10011</v>
       </c>
@@ -1448,24 +1375,23 @@
       <c r="D14" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>77</v>
+      <c r="E14" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="G14" s="3">
         <v>100009</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>10012</v>
       </c>
@@ -1475,24 +1401,23 @@
       <c r="D15" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>78</v>
+      <c r="E15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="G15" s="3">
         <v>999999</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>10013</v>
       </c>
@@ -1502,24 +1427,23 @@
       <c r="D16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>79</v>
+      <c r="E16" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="G16" s="3">
         <v>100011</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>10014</v>
       </c>
@@ -1529,24 +1453,23 @@
       <c r="D17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>107</v>
+      <c r="E17" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>104</v>
       </c>
       <c r="G17" s="3">
         <v>999999</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>10015</v>
       </c>
@@ -1556,24 +1479,23 @@
       <c r="D18" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>80</v>
+      <c r="E18" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>77</v>
       </c>
       <c r="G18" s="3">
         <v>100013</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>10016</v>
       </c>
@@ -1583,24 +1505,23 @@
       <c r="D19" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>81</v>
+      <c r="E19" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="G19" s="3">
         <v>999999</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>10017</v>
       </c>
@@ -1610,24 +1531,23 @@
       <c r="D20" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>82</v>
+      <c r="E20" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="G20" s="3">
         <v>100015</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>10018</v>
       </c>
@@ -1637,24 +1557,23 @@
       <c r="D21" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>83</v>
+      <c r="E21" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="G21" s="3">
         <v>999999</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>10019</v>
       </c>
@@ -1664,24 +1583,23 @@
       <c r="D22" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>84</v>
+      <c r="E22" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="G22" s="3">
         <v>999999</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>10020</v>
       </c>
@@ -1691,49 +1609,47 @@
       <c r="D23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>68</v>
+      <c r="E23" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="G23" s="3">
         <v>100000</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>99999</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="16">
+        <v>105</v>
+      </c>
+      <c r="G24" s="14">
         <v>-1</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="J24" s="4"/>
+        <v>125</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E847F15-AB9A-469D-A2E1-AF41CD9BB3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93361F6-7505-40F0-AD1F-F5FD39B4EF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="2890" windowWidth="40970" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4670" windowWidth="38610" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="121">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -238,14 +238,6 @@
     <t>常驻场景</t>
   </si>
   <si>
-    <t>世界地图</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WordScene+WordScene</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ScenePath</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -402,10 +394,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WordScene+WordSceneDesc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PermanentSceneType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -418,9 +406,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WordScene</t>
-  </si>
-  <si>
     <t>SceneApartmentLivingRoomKitchenTexture</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -494,10 +479,6 @@
   </si>
   <si>
     <t>SceneCafeTexture</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WordSceneTexture</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -567,7 +548,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -657,22 +638,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF1F2329"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF1F2329"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -711,9 +681,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1005,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
@@ -1035,7 +1002,7 @@
         <v>52</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>54</v>
@@ -1063,7 +1030,7 @@
       <c r="E2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="14" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -1072,8 +1039,8 @@
       <c r="H2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="16" t="s">
-        <v>102</v>
+      <c r="I2" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1093,7 +1060,7 @@
         <v>53</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>55</v>
@@ -1116,19 +1083,19 @@
         <v>32</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G4" s="3">
-        <v>999999</v>
+        <v>-1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1142,19 +1109,19 @@
         <v>33</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3">
-        <v>100000</v>
+        <v>-1</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I5" s="17" t="s">
         <v>103</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1168,19 +1135,19 @@
         <v>34</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G6" s="3">
-        <v>100000</v>
+        <v>-1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1194,19 +1161,19 @@
         <v>35</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3">
-        <v>100000</v>
+        <v>-1</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>103</v>
+        <v>105</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1220,19 +1187,19 @@
         <v>36</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G8" s="3">
-        <v>999999</v>
+        <v>-1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1246,19 +1213,19 @@
         <v>37</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G9" s="3">
-        <v>100004</v>
+        <v>-1</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -1272,19 +1239,19 @@
         <v>38</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G10" s="3">
-        <v>100004</v>
+        <v>-1</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1298,19 +1265,19 @@
         <v>39</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G11" s="3">
-        <v>100004</v>
+        <v>-1</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1324,19 +1291,19 @@
         <v>40</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G12" s="3">
-        <v>100004</v>
+        <v>-1</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>103</v>
+        <v>110</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1350,19 +1317,19 @@
         <v>41</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G13" s="3">
-        <v>999999</v>
+        <v>-1</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>103</v>
+        <v>111</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1376,19 +1343,19 @@
         <v>42</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G14" s="3">
-        <v>100009</v>
+        <v>-1</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>103</v>
+        <v>112</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1402,19 +1369,19 @@
         <v>43</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G15" s="3">
-        <v>999999</v>
+        <v>-1</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1428,19 +1395,19 @@
         <v>44</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G16" s="3">
-        <v>100011</v>
+        <v>-1</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>103</v>
+        <v>114</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
@@ -1454,19 +1421,19 @@
         <v>45</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G17" s="3">
-        <v>999999</v>
+        <v>-1</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>103</v>
+        <v>115</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
@@ -1480,19 +1447,19 @@
         <v>46</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G18" s="3">
-        <v>100013</v>
+        <v>-1</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>103</v>
+        <v>116</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
@@ -1506,19 +1473,19 @@
         <v>47</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G19" s="3">
-        <v>999999</v>
+        <v>-1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>103</v>
+        <v>117</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
@@ -1532,19 +1499,19 @@
         <v>48</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G20" s="3">
-        <v>100015</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>103</v>
+        <v>118</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
@@ -1558,19 +1525,19 @@
         <v>49</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G21" s="3">
-        <v>999999</v>
+        <v>-1</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>103</v>
+        <v>119</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
@@ -1584,19 +1551,19 @@
         <v>50</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G22" s="3">
-        <v>999999</v>
+        <v>-1</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>103</v>
+        <v>120</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
@@ -1610,45 +1577,19 @@
         <v>33</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G23" s="3">
-        <v>100000</v>
+        <v>-1</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I23" s="17" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="1">
-        <v>99999</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G24" s="14">
-        <v>-1</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>103</v>
+      <c r="I23" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93361F6-7505-40F0-AD1F-F5FD39B4EF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F92B09-20B1-401F-8E32-E278F41B564C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4670" windowWidth="38610" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11680" yWindow="5160" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="124">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -479,6 +479,17 @@
   </si>
   <si>
     <t>SceneCafeTexture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActiveNpcID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=+),long</t>
+  </si>
+  <si>
+    <t>活动的NPC列表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -548,7 +559,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -638,11 +649,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -690,6 +716,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -972,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
@@ -983,9 +1012,10 @@
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="16.58203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1013,8 +1043,11 @@
       <c r="I1" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1042,8 +1075,11 @@
       <c r="I2" s="15" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1071,8 +1107,11 @@
       <c r="I3" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -1097,8 +1136,11 @@
       <c r="I4" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -1123,8 +1165,11 @@
       <c r="I5" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -1149,8 +1194,11 @@
       <c r="I6" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -1175,8 +1223,11 @@
       <c r="I7" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>10005</v>
       </c>
@@ -1201,8 +1252,11 @@
       <c r="I8" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>10006</v>
       </c>
@@ -1227,8 +1281,11 @@
       <c r="I9" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>10007</v>
       </c>
@@ -1253,8 +1310,11 @@
       <c r="I10" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>10008</v>
       </c>
@@ -1279,8 +1339,11 @@
       <c r="I11" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>10009</v>
       </c>
@@ -1305,8 +1368,11 @@
       <c r="I12" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>10010</v>
       </c>
@@ -1331,8 +1397,11 @@
       <c r="I13" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>10011</v>
       </c>
@@ -1357,8 +1426,11 @@
       <c r="I14" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>10012</v>
       </c>
@@ -1383,8 +1455,11 @@
       <c r="I15" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>10013</v>
       </c>
@@ -1409,8 +1484,11 @@
       <c r="I16" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J16" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>10014</v>
       </c>
@@ -1435,8 +1513,11 @@
       <c r="I17" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J17" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>10015</v>
       </c>
@@ -1461,8 +1542,11 @@
       <c r="I18" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J18" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>10016</v>
       </c>
@@ -1487,8 +1571,11 @@
       <c r="I19" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J19" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>10017</v>
       </c>
@@ -1513,8 +1600,11 @@
       <c r="I20" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J20" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>10018</v>
       </c>
@@ -1539,8 +1629,11 @@
       <c r="I21" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J21" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>10019</v>
       </c>
@@ -1565,8 +1658,11 @@
       <c r="I22" s="16" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J22" s="17">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>10020</v>
       </c>
@@ -1590,6 +1686,9 @@
       </c>
       <c r="I23" s="16" t="s">
         <v>100</v>
+      </c>
+      <c r="J23" s="17">
+        <v>10001</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -125,6 +126,9 @@
     <t>常驻</t>
   </si>
   <si>
+    <t>10003+10007+10014</t>
+  </si>
+  <si>
     <t>女主房间</t>
   </si>
   <si>
@@ -140,6 +144,9 @@
     <t>SceneTheHeroinesRoomTexture</t>
   </si>
   <si>
+    <t>10001+10002</t>
+  </si>
+  <si>
     <t>男主房间</t>
   </si>
   <si>
@@ -275,6 +282,9 @@
     <t>SceneSmallRiverTexture</t>
   </si>
   <si>
+    <t>10021+10028</t>
+  </si>
+  <si>
     <t>酒吧</t>
   </si>
   <si>
@@ -290,6 +300,9 @@
     <t>SceneBarTexture</t>
   </si>
   <si>
+    <t>10004+10009+10018+10022</t>
+  </si>
+  <si>
     <t>赌场</t>
   </si>
   <si>
@@ -335,6 +348,9 @@
     <t>SceneStudioTexture</t>
   </si>
   <si>
+    <t>10015+10026</t>
+  </si>
+  <si>
     <t>会场外</t>
   </si>
   <si>
@@ -365,6 +381,9 @@
     <t>SceneInsideTheVenueTexture</t>
   </si>
   <si>
+    <t>10010+10013</t>
+  </si>
+  <si>
     <t>高级公寓</t>
   </si>
   <si>
@@ -393,6 +412,9 @@
   </si>
   <si>
     <t>SceneCafeTexture</t>
+  </si>
+  <si>
+    <t>10008+10011+10012+10017</t>
   </si>
   <si>
     <t>女主工作室</t>
@@ -408,7 +430,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,38 +440,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -596,7 +601,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -696,12 +701,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1002,19 +1001,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1023,131 +1031,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1155,50 +1154,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1530,683 +1535,695 @@
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="16.5833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="10" max="10" width="29.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
+    <row r="1" ht="16.5" spans="1:10">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
+    <row r="2" ht="16.5" spans="1:10">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
+    <row r="3" ht="16.5" spans="1:10">
+      <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="B4" s="1">
+    <row r="4" ht="16.5" spans="1:10">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14">
         <v>10001</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="8">
         <v>-1</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="16">
-        <v>10001</v>
+      <c r="J4" s="18" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="B5" s="1">
+    <row r="5" ht="16.5" spans="1:10">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14">
         <v>10002</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="E5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="6">
+      <c r="F5" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="8">
         <v>-1</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:10">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:10">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14">
+        <v>10004</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:10">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14">
+        <v>10005</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="18"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:10">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14">
+        <v>10006</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="18">
+        <v>10019</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:10">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14">
+        <v>10007</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="18">
+        <v>10025</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:10">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14">
+        <v>10008</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="18">
+        <v>10027</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:10">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14">
+        <v>10009</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="18">
+        <v>10016</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:10">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14">
+        <v>10010</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="18">
+        <v>10020</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:10">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14">
+        <v>10011</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:10">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14">
+        <v>10012</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:10">
+      <c r="A16" s="13"/>
+      <c r="B16" s="14">
+        <v>10013</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="18">
+        <v>10023</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:10">
+      <c r="A17" s="13"/>
+      <c r="B17" s="14">
+        <v>10014</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="18">
+        <v>10024</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:10">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14">
+        <v>10015</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:10">
+      <c r="A19" s="13"/>
+      <c r="B19" s="14">
+        <v>10016</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="18">
+        <v>10006</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:10">
+      <c r="A20" s="13"/>
+      <c r="B20" s="14">
+        <v>10017</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:10">
+      <c r="A21" s="13"/>
+      <c r="B21" s="14">
+        <v>10018</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="13"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:10">
+      <c r="A22" s="13"/>
+      <c r="B22" s="14">
+        <v>10019</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:10">
+      <c r="A23" s="13"/>
+      <c r="B23" s="14">
+        <v>10020</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="G23" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="1">
-        <v>10003</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="1">
-        <v>10004</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="1">
+      <c r="J23" s="18">
         <v>10005</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1">
-        <v>10006</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="1">
-        <v>10007</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="1">
-        <v>10008</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="1">
-        <v>10009</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="1">
-        <v>10010</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="1">
-        <v>10011</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="1">
-        <v>10012</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="1">
-        <v>10013</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" s="1">
-        <v>10014</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="1">
-        <v>10015</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="1">
-        <v>10016</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G19" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" s="1">
-        <v>10017</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" s="1">
-        <v>10018</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G21" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="1">
-        <v>10019</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="G22" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="16">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="1">
-        <v>10020</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G23" s="6">
-        <v>-1</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="16">
-        <v>10001</v>
       </c>
     </row>
   </sheetData>
@@ -2214,4 +2231,15 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26A5A92-AE1E-4373-AFC7-4821F66D2DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="-5730" yWindow="5890" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="133">
   <si>
     <t>##var</t>
   </si>
@@ -418,19 +424,25 @@
   </si>
   <si>
     <t>女主工作室</t>
+  </si>
+  <si>
+    <t>UnlockConditionsID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁表ID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,166 +454,32 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -614,188 +492,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -900,251 +598,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1157,9 +613,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1184,12 +637,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1205,62 +652,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1518,728 +930,797 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.1666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.5833333333333" customWidth="1"/>
-    <col min="6" max="6" width="96.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="44.58203125" customWidth="1"/>
+    <col min="6" max="6" width="96.83203125" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="16.5833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="29.3333333333333" customWidth="1"/>
+    <col min="9" max="9" width="23.08203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:10">
+    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14">
+    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
         <v>10001</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="18" t="s">
+      <c r="I4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K4" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14">
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
         <v>10002</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="G5" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="18" t="s">
+      <c r="I5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14">
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
         <v>10003</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H6" s="8" t="s">
+      <c r="G6" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:10">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14">
+      <c r="I6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
         <v>10004</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="G7" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="18"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:10">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14">
+      <c r="I7" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
         <v>10005</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="G8" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:10">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14">
+      <c r="I8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
         <v>10006</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H9" s="8" t="s">
+      <c r="G9" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="18">
+      <c r="I9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K9" s="15">
         <v>10019</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:10">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14">
+    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
         <v>10007</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="G10" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="18">
+      <c r="I10" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K10" s="15">
         <v>10025</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:10">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14">
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
         <v>10008</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H11" s="8" t="s">
+      <c r="G11" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="18">
+      <c r="I11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K11" s="15">
         <v>10027</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:10">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14">
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
         <v>10009</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H12" s="8" t="s">
+      <c r="G12" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="18">
+      <c r="I12" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K12" s="15">
         <v>10016</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:10">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14">
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
         <v>10010</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H13" s="8" t="s">
+      <c r="G13" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="I13" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="18">
+      <c r="I13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K13" s="15">
         <v>10020</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:10">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14">
+    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
         <v>10011</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H14" s="8" t="s">
+      <c r="G14" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="I14" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="18" t="s">
+      <c r="I14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K14" s="15" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:10">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14">
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
         <v>10012</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="G15" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H15" s="8" t="s">
+      <c r="G15" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="18" t="s">
+      <c r="I15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K15" s="15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:10">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14">
+    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
         <v>10013</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H16" s="8" t="s">
+      <c r="G16" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I16" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="18">
+      <c r="I16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K16" s="15">
         <v>10023</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:10">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14">
+    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
         <v>10014</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G17" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H17" s="8" t="s">
+      <c r="G17" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="18">
+      <c r="I17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K17" s="15">
         <v>10024</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:10">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14">
+    <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
         <v>10015</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G18" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H18" s="8" t="s">
+      <c r="G18" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="18" t="s">
+      <c r="I18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K18" s="15" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:10">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14">
+    <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
         <v>10016</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="G19" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H19" s="8" t="s">
+      <c r="G19" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="18">
+      <c r="I19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K19" s="15">
         <v>10006</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:10">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14">
+    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
         <v>10017</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H20" s="8" t="s">
+      <c r="G20" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="18" t="s">
+      <c r="I20" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K20" s="15" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:10">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14">
+    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3">
         <v>10018</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="G21" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H21" s="8" t="s">
+      <c r="G21" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="13"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:10">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14">
+      <c r="I21" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3">
         <v>10019</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="G22" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H22" s="8" t="s">
+      <c r="G22" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="18" t="s">
+      <c r="I22" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K22" s="15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:10">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14">
+    <row r="23" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3">
         <v>10020</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H23" s="8" t="s">
+      <c r="G23" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="18">
+      <c r="I23" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K23" s="15">
         <v>10005</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26A5A92-AE1E-4373-AFC7-4821F66D2DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103681A3-2701-4E73-951D-B71CC3AF5F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5730" yWindow="5890" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="64000" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -430,11 +430,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>long</t>
+    <t>解锁表ID</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>解锁表ID</t>
+    <t>条件</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -488,12 +488,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -585,8 +585,21 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFDEE0E3"/>
+        <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FFDEE0E3"/>
       </right>
@@ -602,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -625,13 +638,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -643,23 +650,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -947,7 +951,7 @@
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="23.08203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" style="13" customWidth="1"/>
     <col min="11" max="11" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -973,13 +977,13 @@
       <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>130</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -996,10 +1000,10 @@
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -1008,14 +1012,14 @@
       <c r="G2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="17" t="s">
-        <v>131</v>
+      <c r="J2" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>15</v>
@@ -1031,7 +1035,7 @@
       <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1046,11 +1050,11 @@
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="18" t="s">
-        <v>132</v>
+      <c r="J3" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1061,31 +1065,31 @@
       <c r="B4" s="3">
         <v>10001</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="7">
         <v>-1</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K4" s="15" t="s">
+      <c r="I4" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="15">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1094,31 +1098,31 @@
       <c r="B5" s="3">
         <v>10002</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G5" s="7">
         <v>-1</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K5" s="15" t="s">
+      <c r="I5" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="15">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1127,124 +1131,124 @@
       <c r="B6" s="3">
         <v>10003</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G6" s="7">
         <v>-1</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K6" s="15"/>
+      <c r="I6" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="15">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>10004</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G7" s="7">
         <v>-1</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K7" s="15"/>
+      <c r="I7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>10005</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="7">
         <v>-1</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K8" s="15"/>
+      <c r="I8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>10006</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G9" s="7">
         <v>-1</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K9" s="15">
+      <c r="I9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14">
         <v>10019</v>
       </c>
     </row>
@@ -1253,31 +1257,31 @@
       <c r="B10" s="3">
         <v>10007</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="11" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="7">
         <v>-1</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K10" s="15">
+      <c r="I10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14">
         <v>10025</v>
       </c>
     </row>
@@ -1286,31 +1290,31 @@
       <c r="B11" s="3">
         <v>10008</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="11" t="s">
         <v>67</v>
       </c>
       <c r="G11" s="7">
         <v>-1</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K11" s="15">
+      <c r="I11" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="15">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14">
         <v>10027</v>
       </c>
     </row>
@@ -1319,31 +1323,31 @@
       <c r="B12" s="3">
         <v>10009</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G12" s="7">
         <v>-1</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K12" s="15">
+      <c r="I12" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="15">
+        <v>0</v>
+      </c>
+      <c r="K12" s="14">
         <v>10016</v>
       </c>
     </row>
@@ -1352,31 +1356,31 @@
       <c r="B13" s="3">
         <v>10010</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="7">
         <v>-1</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I13" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K13" s="15">
+      <c r="I13" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0</v>
+      </c>
+      <c r="K13" s="14">
         <v>10020</v>
       </c>
     </row>
@@ -1385,31 +1389,31 @@
       <c r="B14" s="3">
         <v>10011</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="11" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="7">
         <v>-1</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="I14" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K14" s="15" t="s">
+      <c r="I14" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0</v>
+      </c>
+      <c r="K14" s="14" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1418,31 +1422,31 @@
       <c r="B15" s="3">
         <v>10012</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="11" t="s">
         <v>88</v>
       </c>
       <c r="G15" s="7">
         <v>-1</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K15" s="15" t="s">
+      <c r="I15" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="14" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1451,31 +1455,31 @@
       <c r="B16" s="3">
         <v>10013</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="11" t="s">
         <v>94</v>
       </c>
       <c r="G16" s="7">
         <v>-1</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="I16" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K16" s="15">
+      <c r="I16" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0</v>
+      </c>
+      <c r="K16" s="14">
         <v>10023</v>
       </c>
     </row>
@@ -1484,31 +1488,31 @@
       <c r="B17" s="3">
         <v>10014</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="11" t="s">
         <v>99</v>
       </c>
       <c r="G17" s="7">
         <v>-1</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="I17" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K17" s="15">
+      <c r="I17" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="J17" s="15">
+        <v>1</v>
+      </c>
+      <c r="K17" s="14">
         <v>10024</v>
       </c>
     </row>
@@ -1517,31 +1521,31 @@
       <c r="B18" s="3">
         <v>10015</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="11" t="s">
         <v>104</v>
       </c>
       <c r="G18" s="7">
         <v>-1</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="I18" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K18" s="15" t="s">
+      <c r="I18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="15">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1550,31 +1554,31 @@
       <c r="B19" s="3">
         <v>10016</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="11" t="s">
         <v>110</v>
       </c>
       <c r="G19" s="7">
         <v>-1</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K19" s="15">
+      <c r="I19" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14">
         <v>10006</v>
       </c>
     </row>
@@ -1583,31 +1587,31 @@
       <c r="B20" s="3">
         <v>10017</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="11" t="s">
         <v>115</v>
       </c>
       <c r="G20" s="7">
         <v>-1</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K20" s="15" t="s">
+      <c r="I20" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="15">
+        <v>0</v>
+      </c>
+      <c r="K20" s="14" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1616,29 +1620,29 @@
       <c r="B21" s="3">
         <v>10018</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="11" t="s">
         <v>121</v>
       </c>
       <c r="G21" s="7">
         <v>-1</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="19">
-        <v>-1</v>
+      <c r="I21" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="15">
+        <v>0</v>
       </c>
       <c r="K21" s="3"/>
     </row>
@@ -1647,31 +1651,31 @@
       <c r="B22" s="3">
         <v>10019</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="11" t="s">
         <v>126</v>
       </c>
       <c r="G22" s="7">
         <v>-1</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K22" s="15" t="s">
+      <c r="I22" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0</v>
+      </c>
+      <c r="K22" s="14" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1680,31 +1684,31 @@
       <c r="B23" s="3">
         <v>10020</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G23" s="7">
         <v>-1</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K23" s="15">
+      <c r="I23" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="15">
+        <v>0</v>
+      </c>
+      <c r="K23" s="14">
         <v>10005</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103681A3-2701-4E73-951D-B71CC3AF5F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FD64B1-3E90-4D07-B215-FB6CBAB776B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="64000" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57600" yWindow="5085" windowWidth="63705" windowHeight="29775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="136">
   <si>
     <t>##var</t>
   </si>
@@ -435,6 +435,18 @@
   </si>
   <si>
     <t>条件</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NpcSpawnGroupID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机的GroupNPC列表</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000+20001</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -442,7 +454,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,6 +488,21 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -599,23 +626,24 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFDEE0E3"/>
-      </right>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
-        <color rgb="FFDEE0E3"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFDEE0E3"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -656,18 +684,29 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{112EC550-923C-4D08-AB24-D9442170BFCE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -940,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
@@ -953,9 +992,10 @@
     <col min="9" max="9" width="23.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="30.83203125" style="13" customWidth="1"/>
     <col min="11" max="11" width="29.33203125" customWidth="1"/>
+    <col min="12" max="12" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -980,17 +1020,20 @@
       <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L1" s="18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1015,17 +1058,20 @@
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="14" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L2" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -1050,17 +1096,20 @@
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="J3" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="16" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L3" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3">
         <v>10001</v>
@@ -1083,17 +1132,20 @@
       <c r="H4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J4" s="15">
         <v>0</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="16" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L4" s="19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>10002</v>
@@ -1116,17 +1168,18 @@
       <c r="H5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="15">
         <v>0</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L5" s="19"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>10003</v>
@@ -1149,15 +1202,16 @@
       <c r="H6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J6" s="15">
         <v>0</v>
       </c>
-      <c r="K6" s="14"/>
-    </row>
-    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K6" s="16"/>
+      <c r="L6" s="20"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>10004</v>
@@ -1180,15 +1234,16 @@
       <c r="H7" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J7" s="15">
         <v>0</v>
       </c>
-      <c r="K7" s="14"/>
-    </row>
-    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K7" s="16"/>
+      <c r="L7" s="20"/>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>10005</v>
@@ -1211,15 +1266,16 @@
       <c r="H8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="14"/>
-    </row>
-    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K8" s="16"/>
+      <c r="L8" s="20"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3">
         <v>10006</v>
@@ -1242,17 +1298,18 @@
       <c r="H9" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J9" s="15">
         <v>0</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="16">
         <v>10019</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>10007</v>
@@ -1275,17 +1332,18 @@
       <c r="H10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J10" s="15">
         <v>0</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="16">
         <v>10025</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L10" s="20"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3">
         <v>10008</v>
@@ -1308,17 +1366,18 @@
       <c r="H11" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J11" s="15">
         <v>0</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="16">
         <v>10027</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L11" s="20"/>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>10009</v>
@@ -1341,17 +1400,18 @@
       <c r="H12" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J12" s="15">
         <v>0</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="16">
         <v>10016</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L12" s="20"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
         <v>10010</v>
@@ -1374,17 +1434,18 @@
       <c r="H13" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="15">
         <v>0</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="16">
         <v>10020</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L13" s="20"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
         <v>10011</v>
@@ -1407,17 +1468,18 @@
       <c r="H14" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J14" s="15">
         <v>0</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="16" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L14" s="20"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
         <v>10012</v>
@@ -1440,17 +1502,18 @@
       <c r="H15" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J15" s="15">
         <v>0</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
         <v>10013</v>
@@ -1473,17 +1536,18 @@
       <c r="H16" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J16" s="15">
         <v>0</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="16">
         <v>10023</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3">
         <v>10014</v>
@@ -1506,17 +1570,18 @@
       <c r="H17" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="14" t="s">
         <v>132</v>
       </c>
       <c r="J17" s="15">
         <v>1</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="16">
         <v>10024</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
         <v>10015</v>
@@ -1539,17 +1604,18 @@
       <c r="H18" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J18" s="15">
         <v>0</v>
       </c>
-      <c r="K18" s="14" t="s">
+      <c r="K18" s="16" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
         <v>10016</v>
@@ -1572,17 +1638,18 @@
       <c r="H19" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="16" t="s">
+      <c r="I19" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J19" s="15">
         <v>0</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="16">
         <v>10006</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
         <v>10017</v>
@@ -1605,17 +1672,18 @@
       <c r="H20" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="16" t="s">
+      <c r="I20" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J20" s="15">
         <v>0</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="16" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
         <v>10018</v>
@@ -1638,15 +1706,16 @@
       <c r="H21" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="16" t="s">
+      <c r="I21" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J21" s="15">
         <v>0</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K21" s="16"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
         <v>10019</v>
@@ -1669,17 +1738,18 @@
       <c r="H22" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="16" t="s">
+      <c r="I22" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J22" s="15">
         <v>0</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="K22" s="16" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3">
         <v>10020</v>
@@ -1702,15 +1772,16 @@
       <c r="H23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="14" t="s">
         <v>31</v>
       </c>
       <c r="J23" s="15">
         <v>0</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="16">
         <v>10005</v>
       </c>
+      <c r="L23" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FD64B1-3E90-4D07-B215-FB6CBAB776B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA07D13E-4894-481E-82A7-3A3EE949D845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57600" yWindow="5085" windowWidth="63705" windowHeight="29775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -443,10 +443,6 @@
   </si>
   <si>
     <t>随机的GroupNPC列表</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>20000+20001</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1141,8 +1137,8 @@
       <c r="K4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="19" t="s">
-        <v>135</v>
+      <c r="L4" s="18">
+        <v>10001</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D12687A-AA1F-4260-8589-EEDD131A7E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="-10230" yWindow="2570" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -213,14 +219,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,185 +232,45 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,194 +283,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -728,252 +402,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1028,7 +460,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1036,62 +468,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1349,29 +737,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.1666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.5833333333333" customWidth="1"/>
-    <col min="6" max="6" width="96.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="44.58203125" customWidth="1"/>
+    <col min="6" max="6" width="96.83203125" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="23.0833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.8333333333333" style="3" customWidth="1"/>
-    <col min="11" max="11" width="29.3333333333333" customWidth="1"/>
+    <col min="9" max="9" width="23.08203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="29.33203125" customWidth="1"/>
     <col min="12" max="12" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:12">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1409,7 +797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:12">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -1447,7 +835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:12">
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1485,7 +873,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:12">
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A4" s="4"/>
       <c r="B4" s="4">
         <v>10001</v>
@@ -1525,7 +913,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:12">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>10002</v>
@@ -1534,7 +922,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="17" t="str">
-        <f t="shared" ref="D4:D24" si="2">CONCATENATE("WordScene+Scene",B5,"Name")</f>
+        <f t="shared" ref="D5:D24" si="2">CONCATENATE("WordScene+Scene",B5,"Name")</f>
         <v>WordScene+Scene10002Name</v>
       </c>
       <c r="E5" s="17" t="str">
@@ -1542,14 +930,14 @@
         <v>WordScene+Scene10002Text</v>
       </c>
       <c r="F5" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE("Scene",B5,"Path")</f>
         <v>Scene10002Path</v>
       </c>
       <c r="G5" s="8">
         <v>-1</v>
       </c>
       <c r="H5" s="17" t="str">
-        <f t="shared" ref="H4:H24" si="3">CONCATENATE("Scene",B5,"Texture")</f>
+        <f t="shared" ref="H5:H24" si="3">CONCATENATE("Scene",B5,"Texture")</f>
         <v>Scene10002Texture</v>
       </c>
       <c r="I5" s="10" t="s">
@@ -1563,7 +951,7 @@
       </c>
       <c r="L5" s="18"/>
     </row>
-    <row r="6" ht="16.5" spans="1:12">
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>10003</v>
@@ -1580,7 +968,7 @@
         <v>WordScene+Scene10003Text</v>
       </c>
       <c r="F6" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>CONCATENATE("Scene",B6,"Path")</f>
         <v>Scene10003Path</v>
       </c>
       <c r="G6" s="8">
@@ -1599,7 +987,7 @@
       <c r="K6" s="12"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" ht="16.5" spans="1:12">
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>10004</v>
@@ -1635,7 +1023,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" ht="16.5" spans="1:12">
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>10005</v>
@@ -1671,7 +1059,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" ht="16.5" spans="1:12">
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
         <v>10006</v>
@@ -1709,7 +1097,7 @@
       </c>
       <c r="L9" s="19"/>
     </row>
-    <row r="10" ht="16.5" spans="1:12">
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>10007</v>
@@ -1747,7 +1135,7 @@
       </c>
       <c r="L10" s="19"/>
     </row>
-    <row r="11" ht="16.5" spans="1:12">
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="B11" s="4">
         <v>10008</v>
@@ -1785,7 +1173,7 @@
       </c>
       <c r="L11" s="19"/>
     </row>
-    <row r="12" ht="16.5" spans="1:12">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
       <c r="B12" s="4">
         <v>10009</v>
@@ -1823,7 +1211,7 @@
       </c>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" ht="16.5" spans="1:12">
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" s="4">
         <v>10010</v>
@@ -1861,7 +1249,7 @@
       </c>
       <c r="L13" s="19"/>
     </row>
-    <row r="14" ht="16.5" spans="1:12">
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="4">
         <v>10011</v>
@@ -1899,7 +1287,7 @@
       </c>
       <c r="L14" s="19"/>
     </row>
-    <row r="15" ht="16.5" spans="1:12">
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
       <c r="B15" s="4">
         <v>10012</v>
@@ -1937,7 +1325,7 @@
       </c>
       <c r="L15" s="19"/>
     </row>
-    <row r="16" ht="16.5" spans="1:12">
+    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A16" s="4"/>
       <c r="B16" s="4">
         <v>10013</v>
@@ -1975,7 +1363,7 @@
       </c>
       <c r="L16" s="19"/>
     </row>
-    <row r="17" ht="16.5" spans="1:12">
+    <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
       <c r="B17" s="4">
         <v>10014</v>
@@ -2013,7 +1401,7 @@
       </c>
       <c r="L17" s="19"/>
     </row>
-    <row r="18" ht="16.5" spans="1:12">
+    <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A18" s="4"/>
       <c r="B18" s="4">
         <v>10015</v>
@@ -2051,7 +1439,7 @@
       </c>
       <c r="L18" s="19"/>
     </row>
-    <row r="19" ht="16.5" spans="1:12">
+    <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A19" s="4"/>
       <c r="B19" s="4">
         <v>10016</v>
@@ -2089,7 +1477,7 @@
       </c>
       <c r="L19" s="19"/>
     </row>
-    <row r="20" ht="16.5" spans="1:12">
+    <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
       <c r="B20" s="4">
         <v>10017</v>
@@ -2127,7 +1515,7 @@
       </c>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" ht="16.5" spans="1:12">
+    <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A21" s="4"/>
       <c r="B21" s="4">
         <v>10018</v>
@@ -2163,7 +1551,7 @@
       <c r="K21" s="12"/>
       <c r="L21" s="19"/>
     </row>
-    <row r="22" ht="16.5" spans="1:12">
+    <row r="22" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="B22" s="4">
         <v>10019</v>
@@ -2201,7 +1589,7 @@
       </c>
       <c r="L22" s="19"/>
     </row>
-    <row r="23" ht="16.5" spans="1:12">
+    <row r="23" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4">
         <v>10020</v>
@@ -2239,7 +1627,7 @@
       </c>
       <c r="L23" s="19"/>
     </row>
-    <row r="24" ht="16.5" spans="1:12">
+    <row r="24" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A24" s="4"/>
       <c r="B24" s="4">
         <v>10021</v>
@@ -2278,19 +1666,18 @@
       <c r="L24" s="19"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D12687A-AA1F-4260-8589-EEDD131A7E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B584A24-AF22-4CFB-895A-9B30A6706272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10230" yWindow="2570" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B584A24-AF22-4CFB-895A-9B30A6706272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -214,13 +208,22 @@
   </si>
   <si>
     <t>男主工作室</t>
+  </si>
+  <si>
+    <t>会场</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,45 +235,166 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -283,8 +407,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -402,10 +712,252 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -445,7 +997,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -460,26 +1012,70 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -737,29 +1333,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.8333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.58203125" customWidth="1"/>
-    <col min="6" max="6" width="96.83203125" customWidth="1"/>
+    <col min="5" max="5" width="44.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="96.8333333333333" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="23.08203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.83203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.8333333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="29.3333333333333" customWidth="1"/>
     <col min="12" max="12" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="1" ht="16.5" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -797,7 +1393,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="2" ht="16.5" spans="1:12">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -835,7 +1431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" ht="16.5" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -873,7 +1469,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="4" ht="16.5" spans="1:12">
       <c r="A4" s="4"/>
       <c r="B4" s="4">
         <v>10001</v>
@@ -886,11 +1482,11 @@
         <v>WordScene+Scene10001Name</v>
       </c>
       <c r="E4" s="17" t="str">
-        <f t="shared" ref="E4:E24" si="0">CONCATENATE("WordScene+Scene",B4,"Text")</f>
+        <f t="shared" ref="E4:E25" si="0">CONCATENATE("WordScene+Scene",B4,"Text")</f>
         <v>WordScene+Scene10001Text</v>
       </c>
       <c r="F4" s="17" t="str">
-        <f t="shared" ref="F4:F24" si="1">CONCATENATE("Scene",B4,"Path")</f>
+        <f t="shared" ref="F4:F25" si="1">CONCATENATE("Scene",B4,"Path")</f>
         <v>Scene10001Path</v>
       </c>
       <c r="G4" s="8">
@@ -913,7 +1509,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="5" ht="16.5" spans="1:12">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>10002</v>
@@ -922,7 +1518,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="17" t="str">
-        <f t="shared" ref="D5:D24" si="2">CONCATENATE("WordScene+Scene",B5,"Name")</f>
+        <f t="shared" ref="D5:D25" si="2">CONCATENATE("WordScene+Scene",B5,"Name")</f>
         <v>WordScene+Scene10002Name</v>
       </c>
       <c r="E5" s="17" t="str">
@@ -930,14 +1526,14 @@
         <v>WordScene+Scene10002Text</v>
       </c>
       <c r="F5" s="17" t="str">
-        <f>CONCATENATE("Scene",B5,"Path")</f>
+        <f t="shared" si="1"/>
         <v>Scene10002Path</v>
       </c>
       <c r="G5" s="8">
         <v>-1</v>
       </c>
       <c r="H5" s="17" t="str">
-        <f t="shared" ref="H5:H24" si="3">CONCATENATE("Scene",B5,"Texture")</f>
+        <f t="shared" ref="H5:H25" si="3">CONCATENATE("Scene",B5,"Texture")</f>
         <v>Scene10002Texture</v>
       </c>
       <c r="I5" s="10" t="s">
@@ -951,7 +1547,7 @@
       </c>
       <c r="L5" s="18"/>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="6" ht="16.5" spans="1:12">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>10003</v>
@@ -968,7 +1564,7 @@
         <v>WordScene+Scene10003Text</v>
       </c>
       <c r="F6" s="17" t="str">
-        <f>CONCATENATE("Scene",B6,"Path")</f>
+        <f t="shared" si="1"/>
         <v>Scene10003Path</v>
       </c>
       <c r="G6" s="8">
@@ -987,7 +1583,7 @@
       <c r="K6" s="12"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="7" ht="16.5" spans="1:12">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>10004</v>
@@ -1023,7 +1619,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="8" ht="16.5" spans="1:12">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>10005</v>
@@ -1059,7 +1655,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="9" ht="16.5" spans="1:12">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
         <v>10006</v>
@@ -1097,7 +1693,7 @@
       </c>
       <c r="L9" s="19"/>
     </row>
-    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="10" ht="16.5" spans="1:12">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>10007</v>
@@ -1135,7 +1731,7 @@
       </c>
       <c r="L10" s="19"/>
     </row>
-    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="11" ht="16.5" spans="1:12">
       <c r="A11" s="4"/>
       <c r="B11" s="4">
         <v>10008</v>
@@ -1173,7 +1769,7 @@
       </c>
       <c r="L11" s="19"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="12" ht="16.5" spans="1:12">
       <c r="A12" s="4"/>
       <c r="B12" s="4">
         <v>10009</v>
@@ -1211,7 +1807,7 @@
       </c>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="13" ht="16.5" spans="1:12">
       <c r="A13" s="4"/>
       <c r="B13" s="4">
         <v>10010</v>
@@ -1249,7 +1845,7 @@
       </c>
       <c r="L13" s="19"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="14" ht="16.5" spans="1:12">
       <c r="A14" s="4"/>
       <c r="B14" s="4">
         <v>10011</v>
@@ -1287,7 +1883,7 @@
       </c>
       <c r="L14" s="19"/>
     </row>
-    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="15" ht="16.5" spans="1:12">
       <c r="A15" s="4"/>
       <c r="B15" s="4">
         <v>10012</v>
@@ -1325,7 +1921,7 @@
       </c>
       <c r="L15" s="19"/>
     </row>
-    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="16" ht="16.5" spans="1:12">
       <c r="A16" s="4"/>
       <c r="B16" s="4">
         <v>10013</v>
@@ -1363,7 +1959,7 @@
       </c>
       <c r="L16" s="19"/>
     </row>
-    <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="17" ht="16.5" spans="1:12">
       <c r="A17" s="4"/>
       <c r="B17" s="4">
         <v>10014</v>
@@ -1401,7 +1997,7 @@
       </c>
       <c r="L17" s="19"/>
     </row>
-    <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="18" ht="16.5" spans="1:12">
       <c r="A18" s="4"/>
       <c r="B18" s="4">
         <v>10015</v>
@@ -1439,7 +2035,7 @@
       </c>
       <c r="L18" s="19"/>
     </row>
-    <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="19" ht="16.5" spans="1:12">
       <c r="A19" s="4"/>
       <c r="B19" s="4">
         <v>10016</v>
@@ -1477,7 +2073,7 @@
       </c>
       <c r="L19" s="19"/>
     </row>
-    <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="20" ht="16.5" spans="1:12">
       <c r="A20" s="4"/>
       <c r="B20" s="4">
         <v>10017</v>
@@ -1515,7 +2111,7 @@
       </c>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="21" ht="16.5" spans="1:12">
       <c r="A21" s="4"/>
       <c r="B21" s="4">
         <v>10018</v>
@@ -1551,7 +2147,7 @@
       <c r="K21" s="12"/>
       <c r="L21" s="19"/>
     </row>
-    <row r="22" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="22" ht="16.5" spans="1:12">
       <c r="A22" s="4"/>
       <c r="B22" s="4">
         <v>10019</v>
@@ -1589,7 +2185,7 @@
       </c>
       <c r="L22" s="19"/>
     </row>
-    <row r="23" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="23" ht="16.5" spans="1:12">
       <c r="A23" s="4"/>
       <c r="B23" s="4">
         <v>10020</v>
@@ -1627,7 +2223,7 @@
       </c>
       <c r="L23" s="19"/>
     </row>
-    <row r="24" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="24" ht="16.5" spans="1:12">
       <c r="A24" s="4"/>
       <c r="B24" s="4">
         <v>10021</v>
@@ -1665,19 +2261,58 @@
       </c>
       <c r="L24" s="19"/>
     </row>
+    <row r="25" ht="16.5" spans="1:12">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4">
+        <v>10022</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>WordScene+Scene10022Name</v>
+      </c>
+      <c r="E25" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>WordScene+Scene10022Text</v>
+      </c>
+      <c r="F25" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v>Scene10022Path</v>
+      </c>
+      <c r="G25" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H25" s="17" t="str">
+        <f t="shared" si="3"/>
+        <v>Scene10022Texture</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="11">
+        <v>0</v>
+      </c>
+      <c r="K25" s="12">
+        <v>10006</v>
+      </c>
+      <c r="L25" s="19"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <sheetData/>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1493,8 +1493,8 @@
         <v>-1</v>
       </c>
       <c r="H4" s="17" t="str">
-        <f>CONCATENATE("Scene",B4,"Texture")</f>
-        <v>Scene10001Texture</v>
+        <f t="shared" ref="H4:H25" si="2">CONCATENATE("Scene",B4,"Texture.jpg")</f>
+        <v>Scene10001Texture.jpg</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>31</v>
@@ -1518,7 +1518,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="17" t="str">
-        <f t="shared" ref="D5:D25" si="2">CONCATENATE("WordScene+Scene",B5,"Name")</f>
+        <f t="shared" ref="D5:D25" si="3">CONCATENATE("WordScene+Scene",B5,"Name")</f>
         <v>WordScene+Scene10002Name</v>
       </c>
       <c r="E5" s="17" t="str">
@@ -1533,8 +1533,8 @@
         <v>-1</v>
       </c>
       <c r="H5" s="17" t="str">
-        <f t="shared" ref="H5:H25" si="3">CONCATENATE("Scene",B5,"Texture")</f>
-        <v>Scene10002Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10002Texture.jpg</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>31</v>
@@ -1556,7 +1556,7 @@
         <v>35</v>
       </c>
       <c r="D6" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10003Name</v>
       </c>
       <c r="E6" s="17" t="str">
@@ -1571,8 +1571,8 @@
         <v>-1</v>
       </c>
       <c r="H6" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10003Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10003Texture.jpg</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>31</v>
@@ -1592,7 +1592,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10004Name</v>
       </c>
       <c r="E7" s="17" t="str">
@@ -1607,8 +1607,8 @@
         <v>-1</v>
       </c>
       <c r="H7" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10004Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10004Texture.jpg</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>31</v>
@@ -1628,7 +1628,7 @@
         <v>37</v>
       </c>
       <c r="D8" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10005Name</v>
       </c>
       <c r="E8" s="17" t="str">
@@ -1643,8 +1643,8 @@
         <v>-1</v>
       </c>
       <c r="H8" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10005Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10005Texture.jpg</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>31</v>
@@ -1664,7 +1664,7 @@
         <v>38</v>
       </c>
       <c r="D9" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10006Name</v>
       </c>
       <c r="E9" s="17" t="str">
@@ -1679,8 +1679,8 @@
         <v>-1</v>
       </c>
       <c r="H9" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10006Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10006Texture.jpg</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>31</v>
@@ -1702,7 +1702,7 @@
         <v>39</v>
       </c>
       <c r="D10" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10007Name</v>
       </c>
       <c r="E10" s="17" t="str">
@@ -1717,8 +1717,8 @@
         <v>-1</v>
       </c>
       <c r="H10" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10007Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10007Texture.jpg</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10008Name</v>
       </c>
       <c r="E11" s="17" t="str">
@@ -1755,8 +1755,8 @@
         <v>-1</v>
       </c>
       <c r="H11" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10008Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10008Texture.jpg</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>31</v>
@@ -1778,7 +1778,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10009Name</v>
       </c>
       <c r="E12" s="17" t="str">
@@ -1793,8 +1793,8 @@
         <v>-1</v>
       </c>
       <c r="H12" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10009Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10009Texture.jpg</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>31</v>
@@ -1816,7 +1816,7 @@
         <v>42</v>
       </c>
       <c r="D13" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10010Name</v>
       </c>
       <c r="E13" s="17" t="str">
@@ -1831,8 +1831,8 @@
         <v>-1</v>
       </c>
       <c r="H13" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10010Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10010Texture.jpg</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>31</v>
@@ -1854,7 +1854,7 @@
         <v>43</v>
       </c>
       <c r="D14" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10011Name</v>
       </c>
       <c r="E14" s="17" t="str">
@@ -1869,8 +1869,8 @@
         <v>-1</v>
       </c>
       <c r="H14" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10011Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10011Texture.jpg</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>31</v>
@@ -1892,7 +1892,7 @@
         <v>45</v>
       </c>
       <c r="D15" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10012Name</v>
       </c>
       <c r="E15" s="17" t="str">
@@ -1907,8 +1907,8 @@
         <v>-1</v>
       </c>
       <c r="H15" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10012Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10012Texture.jpg</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>31</v>
@@ -1930,7 +1930,7 @@
         <v>47</v>
       </c>
       <c r="D16" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10013Name</v>
       </c>
       <c r="E16" s="17" t="str">
@@ -1945,8 +1945,8 @@
         <v>-1</v>
       </c>
       <c r="H16" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10013Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10013Texture.jpg</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>31</v>
@@ -1968,7 +1968,7 @@
         <v>48</v>
       </c>
       <c r="D17" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10014Name</v>
       </c>
       <c r="E17" s="17" t="str">
@@ -1983,8 +1983,8 @@
         <v>-1</v>
       </c>
       <c r="H17" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10014Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10014Texture.jpg</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>49</v>
@@ -2006,7 +2006,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10015Name</v>
       </c>
       <c r="E18" s="17" t="str">
@@ -2021,8 +2021,8 @@
         <v>-1</v>
       </c>
       <c r="H18" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10015Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10015Texture.jpg</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>31</v>
@@ -2044,7 +2044,7 @@
         <v>52</v>
       </c>
       <c r="D19" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10016Name</v>
       </c>
       <c r="E19" s="17" t="str">
@@ -2059,8 +2059,8 @@
         <v>-1</v>
       </c>
       <c r="H19" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10016Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10016Texture.jpg</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>31</v>
@@ -2082,7 +2082,7 @@
         <v>53</v>
       </c>
       <c r="D20" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10017Name</v>
       </c>
       <c r="E20" s="17" t="str">
@@ -2097,8 +2097,8 @@
         <v>-1</v>
       </c>
       <c r="H20" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10017Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10017Texture.jpg</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>31</v>
@@ -2120,7 +2120,7 @@
         <v>55</v>
       </c>
       <c r="D21" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10018Name</v>
       </c>
       <c r="E21" s="17" t="str">
@@ -2135,8 +2135,8 @@
         <v>-1</v>
       </c>
       <c r="H21" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10018Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10018Texture.jpg</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>31</v>
@@ -2156,7 +2156,7 @@
         <v>56</v>
       </c>
       <c r="D22" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10019Name</v>
       </c>
       <c r="E22" s="17" t="str">
@@ -2171,8 +2171,8 @@
         <v>-1</v>
       </c>
       <c r="H22" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10019Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10019Texture.jpg</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>31</v>
@@ -2194,7 +2194,7 @@
         <v>58</v>
       </c>
       <c r="D23" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10020Name</v>
       </c>
       <c r="E23" s="17" t="str">
@@ -2209,8 +2209,8 @@
         <v>-1</v>
       </c>
       <c r="H23" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10020Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10020Texture.jpg</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>31</v>
@@ -2232,7 +2232,7 @@
         <v>59</v>
       </c>
       <c r="D24" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10021Name</v>
       </c>
       <c r="E24" s="17" t="str">
@@ -2247,8 +2247,8 @@
         <v>-1</v>
       </c>
       <c r="H24" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10021Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10021Texture.jpg</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>31</v>
@@ -2270,7 +2270,7 @@
         <v>60</v>
       </c>
       <c r="D25" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>WordScene+Scene10022Name</v>
       </c>
       <c r="E25" s="17" t="str">
@@ -2285,8 +2285,8 @@
         <v>-1</v>
       </c>
       <c r="H25" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>Scene10022Texture</v>
+        <f t="shared" si="2"/>
+        <v>Scene10022Texture.jpg</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>31</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1493,8 +1493,8 @@
         <v>-1</v>
       </c>
       <c r="H4" s="17" t="str">
-        <f t="shared" ref="H4:H25" si="2">CONCATENATE("Scene",B4,"Texture.jpg")</f>
-        <v>Scene10001Texture.jpg</v>
+        <f>CONCATENATE("Scene",B4,"Texture")</f>
+        <v>Scene10001Texture</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>31</v>
@@ -1518,7 +1518,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="17" t="str">
-        <f t="shared" ref="D5:D25" si="3">CONCATENATE("WordScene+Scene",B5,"Name")</f>
+        <f t="shared" ref="D5:D25" si="2">CONCATENATE("WordScene+Scene",B5,"Name")</f>
         <v>WordScene+Scene10002Name</v>
       </c>
       <c r="E5" s="17" t="str">
@@ -1533,8 +1533,8 @@
         <v>-1</v>
       </c>
       <c r="H5" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10002Texture.jpg</v>
+        <f t="shared" ref="H5:H25" si="3">CONCATENATE("Scene",B5,"Texture")</f>
+        <v>Scene10002Texture</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>31</v>
@@ -1556,7 +1556,7 @@
         <v>35</v>
       </c>
       <c r="D6" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10003Name</v>
       </c>
       <c r="E6" s="17" t="str">
@@ -1571,8 +1571,8 @@
         <v>-1</v>
       </c>
       <c r="H6" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10003Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10003Texture</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>31</v>
@@ -1592,7 +1592,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10004Name</v>
       </c>
       <c r="E7" s="17" t="str">
@@ -1607,8 +1607,8 @@
         <v>-1</v>
       </c>
       <c r="H7" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10004Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10004Texture</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>31</v>
@@ -1628,7 +1628,7 @@
         <v>37</v>
       </c>
       <c r="D8" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10005Name</v>
       </c>
       <c r="E8" s="17" t="str">
@@ -1643,8 +1643,8 @@
         <v>-1</v>
       </c>
       <c r="H8" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10005Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10005Texture</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>31</v>
@@ -1664,7 +1664,7 @@
         <v>38</v>
       </c>
       <c r="D9" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10006Name</v>
       </c>
       <c r="E9" s="17" t="str">
@@ -1679,8 +1679,8 @@
         <v>-1</v>
       </c>
       <c r="H9" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10006Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10006Texture</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>31</v>
@@ -1702,7 +1702,7 @@
         <v>39</v>
       </c>
       <c r="D10" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10007Name</v>
       </c>
       <c r="E10" s="17" t="str">
@@ -1717,8 +1717,8 @@
         <v>-1</v>
       </c>
       <c r="H10" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10007Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10007Texture</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>31</v>
@@ -1740,7 +1740,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10008Name</v>
       </c>
       <c r="E11" s="17" t="str">
@@ -1755,8 +1755,8 @@
         <v>-1</v>
       </c>
       <c r="H11" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10008Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10008Texture</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>31</v>
@@ -1778,7 +1778,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10009Name</v>
       </c>
       <c r="E12" s="17" t="str">
@@ -1793,8 +1793,8 @@
         <v>-1</v>
       </c>
       <c r="H12" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10009Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10009Texture</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>31</v>
@@ -1816,7 +1816,7 @@
         <v>42</v>
       </c>
       <c r="D13" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10010Name</v>
       </c>
       <c r="E13" s="17" t="str">
@@ -1831,8 +1831,8 @@
         <v>-1</v>
       </c>
       <c r="H13" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10010Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10010Texture</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>31</v>
@@ -1854,7 +1854,7 @@
         <v>43</v>
       </c>
       <c r="D14" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10011Name</v>
       </c>
       <c r="E14" s="17" t="str">
@@ -1869,8 +1869,8 @@
         <v>-1</v>
       </c>
       <c r="H14" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10011Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10011Texture</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>31</v>
@@ -1892,7 +1892,7 @@
         <v>45</v>
       </c>
       <c r="D15" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10012Name</v>
       </c>
       <c r="E15" s="17" t="str">
@@ -1907,8 +1907,8 @@
         <v>-1</v>
       </c>
       <c r="H15" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10012Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10012Texture</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>31</v>
@@ -1930,7 +1930,7 @@
         <v>47</v>
       </c>
       <c r="D16" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10013Name</v>
       </c>
       <c r="E16" s="17" t="str">
@@ -1945,8 +1945,8 @@
         <v>-1</v>
       </c>
       <c r="H16" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10013Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10013Texture</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>31</v>
@@ -1968,7 +1968,7 @@
         <v>48</v>
       </c>
       <c r="D17" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10014Name</v>
       </c>
       <c r="E17" s="17" t="str">
@@ -1983,8 +1983,8 @@
         <v>-1</v>
       </c>
       <c r="H17" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10014Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10014Texture</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>49</v>
@@ -2006,7 +2006,7 @@
         <v>50</v>
       </c>
       <c r="D18" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10015Name</v>
       </c>
       <c r="E18" s="17" t="str">
@@ -2021,8 +2021,8 @@
         <v>-1</v>
       </c>
       <c r="H18" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10015Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10015Texture</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>31</v>
@@ -2044,7 +2044,7 @@
         <v>52</v>
       </c>
       <c r="D19" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10016Name</v>
       </c>
       <c r="E19" s="17" t="str">
@@ -2059,8 +2059,8 @@
         <v>-1</v>
       </c>
       <c r="H19" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10016Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10016Texture</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>31</v>
@@ -2082,7 +2082,7 @@
         <v>53</v>
       </c>
       <c r="D20" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10017Name</v>
       </c>
       <c r="E20" s="17" t="str">
@@ -2097,8 +2097,8 @@
         <v>-1</v>
       </c>
       <c r="H20" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10017Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10017Texture</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>31</v>
@@ -2120,7 +2120,7 @@
         <v>55</v>
       </c>
       <c r="D21" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10018Name</v>
       </c>
       <c r="E21" s="17" t="str">
@@ -2135,8 +2135,8 @@
         <v>-1</v>
       </c>
       <c r="H21" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10018Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10018Texture</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>31</v>
@@ -2156,7 +2156,7 @@
         <v>56</v>
       </c>
       <c r="D22" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10019Name</v>
       </c>
       <c r="E22" s="17" t="str">
@@ -2171,8 +2171,8 @@
         <v>-1</v>
       </c>
       <c r="H22" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10019Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10019Texture</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>31</v>
@@ -2194,7 +2194,7 @@
         <v>58</v>
       </c>
       <c r="D23" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10020Name</v>
       </c>
       <c r="E23" s="17" t="str">
@@ -2209,8 +2209,8 @@
         <v>-1</v>
       </c>
       <c r="H23" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10020Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10020Texture</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>31</v>
@@ -2232,7 +2232,7 @@
         <v>59</v>
       </c>
       <c r="D24" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10021Name</v>
       </c>
       <c r="E24" s="17" t="str">
@@ -2247,8 +2247,8 @@
         <v>-1</v>
       </c>
       <c r="H24" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10021Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10021Texture</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>31</v>
@@ -2270,7 +2270,7 @@
         <v>60</v>
       </c>
       <c r="D25" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>WordScene+Scene10022Name</v>
       </c>
       <c r="E25" s="17" t="str">
@@ -2285,8 +2285,8 @@
         <v>-1</v>
       </c>
       <c r="H25" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>Scene10022Texture.jpg</v>
+        <f t="shared" si="3"/>
+        <v>Scene10022Texture</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>31</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3A2E3E-95CE-427C-A79F-30CC50871EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -216,14 +222,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,166 +235,40 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,194 +281,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -712,252 +400,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1012,7 +458,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1020,62 +466,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1333,29 +735,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.1666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.5833333333333" customWidth="1"/>
-    <col min="6" max="6" width="96.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="44.58203125" customWidth="1"/>
+    <col min="6" max="6" width="96.83203125" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="23.0833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.8333333333333" style="3" customWidth="1"/>
-    <col min="11" max="11" width="29.3333333333333" customWidth="1"/>
+    <col min="9" max="9" width="23.08203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="29.33203125" customWidth="1"/>
     <col min="12" max="12" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:12">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1393,7 +795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:12">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -1431,7 +833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:12">
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1469,7 +871,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:12">
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A4" s="4"/>
       <c r="B4" s="4">
         <v>10001</v>
@@ -1493,8 +895,8 @@
         <v>-1</v>
       </c>
       <c r="H4" s="17" t="str">
-        <f>CONCATENATE("Scene",B4,"Texture")</f>
-        <v>Scene10001Texture</v>
+        <f>CONCATENATE("Scene",B4,"Texture.jpg")</f>
+        <v>Scene10001Texture.jpg</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>31</v>
@@ -1509,7 +911,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:12">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>10002</v>
@@ -1533,8 +935,8 @@
         <v>-1</v>
       </c>
       <c r="H5" s="17" t="str">
-        <f t="shared" ref="H5:H25" si="3">CONCATENATE("Scene",B5,"Texture")</f>
-        <v>Scene10002Texture</v>
+        <f t="shared" ref="H5:H25" si="3">CONCATENATE("Scene",B5,"Texture.jpg")</f>
+        <v>Scene10002Texture.jpg</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>31</v>
@@ -1547,7 +949,7 @@
       </c>
       <c r="L5" s="18"/>
     </row>
-    <row r="6" ht="16.5" spans="1:12">
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>10003</v>
@@ -1572,7 +974,7 @@
       </c>
       <c r="H6" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10003Texture</v>
+        <v>Scene10003Texture.jpg</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>31</v>
@@ -1583,7 +985,7 @@
       <c r="K6" s="12"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" ht="16.5" spans="1:12">
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>10004</v>
@@ -1608,7 +1010,7 @@
       </c>
       <c r="H7" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10004Texture</v>
+        <v>Scene10004Texture.jpg</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>31</v>
@@ -1619,7 +1021,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" ht="16.5" spans="1:12">
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>10005</v>
@@ -1644,7 +1046,7 @@
       </c>
       <c r="H8" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10005Texture</v>
+        <v>Scene10005Texture.jpg</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>31</v>
@@ -1655,7 +1057,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" ht="16.5" spans="1:12">
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
         <v>10006</v>
@@ -1680,7 +1082,7 @@
       </c>
       <c r="H9" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10006Texture</v>
+        <v>Scene10006Texture.jpg</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>31</v>
@@ -1693,7 +1095,7 @@
       </c>
       <c r="L9" s="19"/>
     </row>
-    <row r="10" ht="16.5" spans="1:12">
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>10007</v>
@@ -1718,7 +1120,7 @@
       </c>
       <c r="H10" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10007Texture</v>
+        <v>Scene10007Texture.jpg</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>31</v>
@@ -1731,7 +1133,7 @@
       </c>
       <c r="L10" s="19"/>
     </row>
-    <row r="11" ht="16.5" spans="1:12">
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="B11" s="4">
         <v>10008</v>
@@ -1756,7 +1158,7 @@
       </c>
       <c r="H11" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10008Texture</v>
+        <v>Scene10008Texture.jpg</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>31</v>
@@ -1769,7 +1171,7 @@
       </c>
       <c r="L11" s="19"/>
     </row>
-    <row r="12" ht="16.5" spans="1:12">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
       <c r="B12" s="4">
         <v>10009</v>
@@ -1794,7 +1196,7 @@
       </c>
       <c r="H12" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10009Texture</v>
+        <v>Scene10009Texture.jpg</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>31</v>
@@ -1807,7 +1209,7 @@
       </c>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" ht="16.5" spans="1:12">
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" s="4">
         <v>10010</v>
@@ -1832,7 +1234,7 @@
       </c>
       <c r="H13" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10010Texture</v>
+        <v>Scene10010Texture.jpg</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>31</v>
@@ -1845,7 +1247,7 @@
       </c>
       <c r="L13" s="19"/>
     </row>
-    <row r="14" ht="16.5" spans="1:12">
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="4">
         <v>10011</v>
@@ -1870,7 +1272,7 @@
       </c>
       <c r="H14" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10011Texture</v>
+        <v>Scene10011Texture.jpg</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>31</v>
@@ -1883,7 +1285,7 @@
       </c>
       <c r="L14" s="19"/>
     </row>
-    <row r="15" ht="16.5" spans="1:12">
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
       <c r="B15" s="4">
         <v>10012</v>
@@ -1908,7 +1310,7 @@
       </c>
       <c r="H15" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10012Texture</v>
+        <v>Scene10012Texture.jpg</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>31</v>
@@ -1921,7 +1323,7 @@
       </c>
       <c r="L15" s="19"/>
     </row>
-    <row r="16" ht="16.5" spans="1:12">
+    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A16" s="4"/>
       <c r="B16" s="4">
         <v>10013</v>
@@ -1946,7 +1348,7 @@
       </c>
       <c r="H16" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10013Texture</v>
+        <v>Scene10013Texture.jpg</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>31</v>
@@ -1959,7 +1361,7 @@
       </c>
       <c r="L16" s="19"/>
     </row>
-    <row r="17" ht="16.5" spans="1:12">
+    <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
       <c r="B17" s="4">
         <v>10014</v>
@@ -1984,7 +1386,7 @@
       </c>
       <c r="H17" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10014Texture</v>
+        <v>Scene10014Texture.jpg</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>49</v>
@@ -1997,7 +1399,7 @@
       </c>
       <c r="L17" s="19"/>
     </row>
-    <row r="18" ht="16.5" spans="1:12">
+    <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A18" s="4"/>
       <c r="B18" s="4">
         <v>10015</v>
@@ -2022,7 +1424,7 @@
       </c>
       <c r="H18" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10015Texture</v>
+        <v>Scene10015Texture.jpg</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>31</v>
@@ -2035,7 +1437,7 @@
       </c>
       <c r="L18" s="19"/>
     </row>
-    <row r="19" ht="16.5" spans="1:12">
+    <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A19" s="4"/>
       <c r="B19" s="4">
         <v>10016</v>
@@ -2060,7 +1462,7 @@
       </c>
       <c r="H19" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10016Texture</v>
+        <v>Scene10016Texture.jpg</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>31</v>
@@ -2073,7 +1475,7 @@
       </c>
       <c r="L19" s="19"/>
     </row>
-    <row r="20" ht="16.5" spans="1:12">
+    <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
       <c r="B20" s="4">
         <v>10017</v>
@@ -2098,7 +1500,7 @@
       </c>
       <c r="H20" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10017Texture</v>
+        <v>Scene10017Texture.jpg</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>31</v>
@@ -2111,7 +1513,7 @@
       </c>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" ht="16.5" spans="1:12">
+    <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A21" s="4"/>
       <c r="B21" s="4">
         <v>10018</v>
@@ -2136,7 +1538,7 @@
       </c>
       <c r="H21" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10018Texture</v>
+        <v>Scene10018Texture.jpg</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>31</v>
@@ -2147,7 +1549,7 @@
       <c r="K21" s="12"/>
       <c r="L21" s="19"/>
     </row>
-    <row r="22" ht="16.5" spans="1:12">
+    <row r="22" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="B22" s="4">
         <v>10019</v>
@@ -2172,7 +1574,7 @@
       </c>
       <c r="H22" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10019Texture</v>
+        <v>Scene10019Texture.jpg</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>31</v>
@@ -2185,7 +1587,7 @@
       </c>
       <c r="L22" s="19"/>
     </row>
-    <row r="23" ht="16.5" spans="1:12">
+    <row r="23" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4">
         <v>10020</v>
@@ -2210,7 +1612,7 @@
       </c>
       <c r="H23" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10020Texture</v>
+        <v>Scene10020Texture.jpg</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>31</v>
@@ -2223,7 +1625,7 @@
       </c>
       <c r="L23" s="19"/>
     </row>
-    <row r="24" ht="16.5" spans="1:12">
+    <row r="24" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A24" s="4"/>
       <c r="B24" s="4">
         <v>10021</v>
@@ -2248,7 +1650,7 @@
       </c>
       <c r="H24" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10021Texture</v>
+        <v>Scene10021Texture.jpg</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>31</v>
@@ -2261,7 +1663,7 @@
       </c>
       <c r="L24" s="19"/>
     </row>
-    <row r="25" ht="16.5" spans="1:12">
+    <row r="25" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A25" s="4"/>
       <c r="B25" s="4">
         <v>10022</v>
@@ -2286,7 +1688,7 @@
       </c>
       <c r="H25" s="17" t="str">
         <f t="shared" si="3"/>
-        <v>Scene10022Texture</v>
+        <v>Scene10022Texture.jpg</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>31</v>
@@ -2300,19 +1702,18 @@
       <c r="L25" s="19"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3A2E3E-95CE-427C-A79F-30CC50871EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -178,6 +172,9 @@
   </si>
   <si>
     <t>赌场</t>
+  </si>
+  <si>
+    <t>10023+10029+10030+10031</t>
   </si>
   <si>
     <t>周边工厂</t>
@@ -222,8 +219,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,40 +238,166 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,8 +410,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -400,10 +715,252 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -458,7 +1015,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -466,18 +1023,62 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -735,29 +1336,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.8333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.58203125" customWidth="1"/>
-    <col min="6" max="6" width="96.83203125" customWidth="1"/>
+    <col min="5" max="5" width="44.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="96.8333333333333" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="23.08203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.83203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.8333333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="29.3333333333333" customWidth="1"/>
     <col min="12" max="12" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="1" ht="16.5" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -795,7 +1396,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="2" ht="16.5" spans="1:12">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -833,7 +1434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" ht="16.5" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -871,7 +1472,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="4" ht="16.5" spans="1:12">
       <c r="A4" s="4"/>
       <c r="B4" s="4">
         <v>10001</v>
@@ -911,7 +1512,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="5" ht="16.5" spans="1:12">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>10002</v>
@@ -949,7 +1550,7 @@
       </c>
       <c r="L5" s="18"/>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="6" ht="16.5" spans="1:12">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>10003</v>
@@ -985,7 +1586,7 @@
       <c r="K6" s="12"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="7" ht="16.5" spans="1:12">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>10004</v>
@@ -1021,7 +1622,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="8" ht="16.5" spans="1:12">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>10005</v>
@@ -1057,7 +1658,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="9" ht="16.5" spans="1:12">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
         <v>10006</v>
@@ -1095,7 +1696,7 @@
       </c>
       <c r="L9" s="19"/>
     </row>
-    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="10" ht="16.5" spans="1:12">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>10007</v>
@@ -1133,7 +1734,7 @@
       </c>
       <c r="L10" s="19"/>
     </row>
-    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="11" ht="16.5" spans="1:12">
       <c r="A11" s="4"/>
       <c r="B11" s="4">
         <v>10008</v>
@@ -1171,7 +1772,7 @@
       </c>
       <c r="L11" s="19"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="12" ht="16.5" spans="1:12">
       <c r="A12" s="4"/>
       <c r="B12" s="4">
         <v>10009</v>
@@ -1209,7 +1810,7 @@
       </c>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="13" ht="16.5" spans="1:12">
       <c r="A13" s="4"/>
       <c r="B13" s="4">
         <v>10010</v>
@@ -1247,7 +1848,7 @@
       </c>
       <c r="L13" s="19"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="14" ht="16.5" spans="1:12">
       <c r="A14" s="4"/>
       <c r="B14" s="4">
         <v>10011</v>
@@ -1285,7 +1886,7 @@
       </c>
       <c r="L14" s="19"/>
     </row>
-    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="15" ht="16.5" spans="1:12">
       <c r="A15" s="4"/>
       <c r="B15" s="4">
         <v>10012</v>
@@ -1323,7 +1924,7 @@
       </c>
       <c r="L15" s="19"/>
     </row>
-    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="16" ht="16.5" spans="1:12">
       <c r="A16" s="4"/>
       <c r="B16" s="4">
         <v>10013</v>
@@ -1356,18 +1957,18 @@
       <c r="J16" s="11">
         <v>0</v>
       </c>
-      <c r="K16" s="12">
-        <v>10023</v>
+      <c r="K16" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="L16" s="19"/>
     </row>
-    <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="17" ht="16.5" spans="1:12">
       <c r="A17" s="4"/>
       <c r="B17" s="4">
         <v>10014</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1389,7 +1990,7 @@
         <v>Scene10014Texture.jpg</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J17" s="11">
         <v>1</v>
@@ -1399,13 +2000,13 @@
       </c>
       <c r="L17" s="19"/>
     </row>
-    <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="18" ht="16.5" spans="1:12">
       <c r="A18" s="4"/>
       <c r="B18" s="4">
         <v>10015</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1433,17 +2034,17 @@
         <v>0</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L18" s="19"/>
     </row>
-    <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="19" ht="16.5" spans="1:12">
       <c r="A19" s="4"/>
       <c r="B19" s="4">
         <v>10016</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1475,13 +2076,13 @@
       </c>
       <c r="L19" s="19"/>
     </row>
-    <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="20" ht="16.5" spans="1:12">
       <c r="A20" s="4"/>
       <c r="B20" s="4">
         <v>10017</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D20" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1509,17 +2110,17 @@
         <v>0</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="21" ht="16.5" spans="1:12">
       <c r="A21" s="4"/>
       <c r="B21" s="4">
         <v>10018</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1549,13 +2150,13 @@
       <c r="K21" s="12"/>
       <c r="L21" s="19"/>
     </row>
-    <row r="22" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="22" ht="16.5" spans="1:12">
       <c r="A22" s="4"/>
       <c r="B22" s="4">
         <v>10019</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D22" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1583,17 +2184,17 @@
         <v>0</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L22" s="19"/>
     </row>
-    <row r="23" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="23" ht="16.5" spans="1:12">
       <c r="A23" s="4"/>
       <c r="B23" s="4">
         <v>10020</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1625,13 +2226,13 @@
       </c>
       <c r="L23" s="19"/>
     </row>
-    <row r="24" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="24" ht="16.5" spans="1:12">
       <c r="A24" s="4"/>
       <c r="B24" s="4">
         <v>10021</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1663,13 +2264,13 @@
       </c>
       <c r="L24" s="19"/>
     </row>
-    <row r="25" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="25" ht="16.5" spans="1:12">
       <c r="A25" s="4"/>
       <c r="B25" s="4">
         <v>10022</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" s="17" t="str">
         <f t="shared" si="2"/>
@@ -1702,18 +2303,19 @@
       <c r="L25" s="19"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <sheetData/>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_DA13E7C60FDD8C43C222A6F5C8BFF7A4B7DA8CE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="4560" yWindow="2920" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -219,14 +225,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,166 +238,40 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,194 +284,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -715,252 +403,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1015,7 +461,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1023,62 +469,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1336,29 +738,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.1666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.5833333333333" customWidth="1"/>
-    <col min="6" max="6" width="96.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="44.58203125" customWidth="1"/>
+    <col min="6" max="6" width="96.83203125" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="23.0833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.8333333333333" style="3" customWidth="1"/>
-    <col min="11" max="11" width="29.3333333333333" customWidth="1"/>
+    <col min="9" max="9" width="23.08203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="29.33203125" customWidth="1"/>
     <col min="12" max="12" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:12">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1396,7 +798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:12">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -1434,7 +836,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:12">
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1472,7 +874,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:12">
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A4" s="4"/>
       <c r="B4" s="4">
         <v>10001</v>
@@ -1512,7 +914,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:12">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>10002</v>
@@ -1550,7 +952,7 @@
       </c>
       <c r="L5" s="18"/>
     </row>
-    <row r="6" ht="16.5" spans="1:12">
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>10003</v>
@@ -1586,7 +988,7 @@
       <c r="K6" s="12"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" ht="16.5" spans="1:12">
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>10004</v>
@@ -1622,7 +1024,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" ht="16.5" spans="1:12">
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>10005</v>
@@ -1658,7 +1060,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" ht="16.5" spans="1:12">
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
         <v>10006</v>
@@ -1696,7 +1098,7 @@
       </c>
       <c r="L9" s="19"/>
     </row>
-    <row r="10" ht="16.5" spans="1:12">
+    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>10007</v>
@@ -1734,7 +1136,7 @@
       </c>
       <c r="L10" s="19"/>
     </row>
-    <row r="11" ht="16.5" spans="1:12">
+    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="B11" s="4">
         <v>10008</v>
@@ -1772,7 +1174,7 @@
       </c>
       <c r="L11" s="19"/>
     </row>
-    <row r="12" ht="16.5" spans="1:12">
+    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
       <c r="B12" s="4">
         <v>10009</v>
@@ -1810,7 +1212,7 @@
       </c>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" ht="16.5" spans="1:12">
+    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" s="4">
         <v>10010</v>
@@ -1848,7 +1250,7 @@
       </c>
       <c r="L13" s="19"/>
     </row>
-    <row r="14" ht="16.5" spans="1:12">
+    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="4">
         <v>10011</v>
@@ -1886,7 +1288,7 @@
       </c>
       <c r="L14" s="19"/>
     </row>
-    <row r="15" ht="16.5" spans="1:12">
+    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
       <c r="B15" s="4">
         <v>10012</v>
@@ -1924,7 +1326,7 @@
       </c>
       <c r="L15" s="19"/>
     </row>
-    <row r="16" ht="16.5" spans="1:12">
+    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A16" s="4"/>
       <c r="B16" s="4">
         <v>10013</v>
@@ -1962,7 +1364,7 @@
       </c>
       <c r="L16" s="19"/>
     </row>
-    <row r="17" ht="16.5" spans="1:12">
+    <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
       <c r="B17" s="4">
         <v>10014</v>
@@ -2000,7 +1402,7 @@
       </c>
       <c r="L17" s="19"/>
     </row>
-    <row r="18" ht="16.5" spans="1:12">
+    <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A18" s="4"/>
       <c r="B18" s="4">
         <v>10015</v>
@@ -2038,7 +1440,7 @@
       </c>
       <c r="L18" s="19"/>
     </row>
-    <row r="19" ht="16.5" spans="1:12">
+    <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A19" s="4"/>
       <c r="B19" s="4">
         <v>10016</v>
@@ -2076,7 +1478,7 @@
       </c>
       <c r="L19" s="19"/>
     </row>
-    <row r="20" ht="16.5" spans="1:12">
+    <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
       <c r="B20" s="4">
         <v>10017</v>
@@ -2114,7 +1516,7 @@
       </c>
       <c r="L20" s="19"/>
     </row>
-    <row r="21" ht="16.5" spans="1:12">
+    <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A21" s="4"/>
       <c r="B21" s="4">
         <v>10018</v>
@@ -2150,7 +1552,7 @@
       <c r="K21" s="12"/>
       <c r="L21" s="19"/>
     </row>
-    <row r="22" ht="16.5" spans="1:12">
+    <row r="22" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="B22" s="4">
         <v>10019</v>
@@ -2188,7 +1590,7 @@
       </c>
       <c r="L22" s="19"/>
     </row>
-    <row r="23" ht="16.5" spans="1:12">
+    <row r="23" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4">
         <v>10020</v>
@@ -2226,7 +1628,7 @@
       </c>
       <c r="L23" s="19"/>
     </row>
-    <row r="24" ht="16.5" spans="1:12">
+    <row r="24" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A24" s="4"/>
       <c r="B24" s="4">
         <v>10021</v>
@@ -2264,7 +1666,7 @@
       </c>
       <c r="L24" s="19"/>
     </row>
-    <row r="25" ht="16.5" spans="1:12">
+    <row r="25" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A25" s="4"/>
       <c r="B25" s="4">
         <v>10022</v>
@@ -2303,19 +1705,18 @@
       <c r="L25" s="19"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DA13E7C60FDD8C43C222A6F5C8BFF7A4B7DA8CE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35E7D0B-95B4-4454-8FF3-720D25491EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="2920" windowWidth="30580" windowHeight="18680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3130" yWindow="1270" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -220,6 +220,21 @@
   </si>
   <si>
     <t>会场</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景默认的UI界面</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GarmentMakingCommonUI</t>
+  </si>
+  <si>
+    <t>SceneUI</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -408,7 +423,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -467,6 +482,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -744,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
@@ -758,9 +776,10 @@
     <col min="10" max="10" width="30.83203125" style="3" customWidth="1"/>
     <col min="11" max="11" width="29.33203125" customWidth="1"/>
     <col min="12" max="12" width="21.25" customWidth="1"/>
+    <col min="13" max="13" width="24.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -797,8 +816,11 @@
       <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M1" s="21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -835,8 +857,11 @@
       <c r="L2" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M2" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -873,8 +898,11 @@
       <c r="L3" s="15" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="M3" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A4" s="4"/>
       <c r="B4" s="4">
         <v>10001</v>
@@ -914,7 +942,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>10002</v>
@@ -952,7 +980,7 @@
       </c>
       <c r="L5" s="18"/>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>10003</v>
@@ -987,8 +1015,11 @@
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="19"/>
-    </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="M6" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>10004</v>
@@ -1024,7 +1055,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>10005</v>
@@ -1060,7 +1091,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
         <v>10006</v>
@@ -1098,7 +1129,7 @@
       </c>
       <c r="L9" s="19"/>
     </row>
-    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>10007</v>
@@ -1136,7 +1167,7 @@
       </c>
       <c r="L10" s="19"/>
     </row>
-    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="B11" s="4">
         <v>10008</v>
@@ -1174,7 +1205,7 @@
       </c>
       <c r="L11" s="19"/>
     </row>
-    <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
       <c r="B12" s="4">
         <v>10009</v>
@@ -1212,7 +1243,7 @@
       </c>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A13" s="4"/>
       <c r="B13" s="4">
         <v>10010</v>
@@ -1250,7 +1281,7 @@
       </c>
       <c r="L13" s="19"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
       <c r="B14" s="4">
         <v>10011</v>
@@ -1288,7 +1319,7 @@
       </c>
       <c r="L14" s="19"/>
     </row>
-    <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A15" s="4"/>
       <c r="B15" s="4">
         <v>10012</v>
@@ -1326,7 +1357,7 @@
       </c>
       <c r="L15" s="19"/>
     </row>
-    <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A16" s="4"/>
       <c r="B16" s="4">
         <v>10013</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35E7D0B-95B4-4454-8FF3-720D25491EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3130" yWindow="1270" windowWidth="31320" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="小场景" sheetId="1" r:id="rId1"/>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -72,6 +66,9 @@
     <t>NpcSpawnGroupID</t>
   </si>
   <si>
+    <t>SceneUI</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -126,6 +123,9 @@
     <t>随机的GroupNPC列表</t>
   </si>
   <si>
+    <t>场景默认的UI界面</t>
+  </si>
+  <si>
     <t>公寓客厅厨房</t>
   </si>
   <si>
@@ -144,6 +144,9 @@
     <t>男主房间</t>
   </si>
   <si>
+    <t>GarmentMakingCommonUI</t>
+  </si>
+  <si>
     <t>卫浴间</t>
   </si>
   <si>
@@ -220,28 +223,19 @@
   </si>
   <si>
     <t>会场</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景默认的UI界面</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>GarmentMakingCommonUI</t>
-  </si>
-  <si>
-    <t>SceneUI</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,40 +247,173 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,8 +426,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -418,9 +731,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
@@ -464,6 +1019,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -476,29 +1034,70 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -756,30 +1355,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="15.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.8333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.58203125" customWidth="1"/>
-    <col min="6" max="6" width="96.83203125" customWidth="1"/>
+    <col min="5" max="5" width="44.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="96.8333333333333" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="23.08203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.83203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.8333333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="39.9166666666667" customWidth="1"/>
     <col min="12" max="12" width="21.25" customWidth="1"/>
-    <col min="13" max="13" width="24.58203125" customWidth="1"/>
+    <col min="13" max="13" width="24.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="1" ht="16.5" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -816,310 +1415,310 @@
       <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="M1" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="H2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="I2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="16" t="s">
         <v>21</v>
       </c>
+      <c r="D3" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="E3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L3" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:13">
       <c r="A4" s="4"/>
       <c r="B4" s="4">
         <v>10001</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="17" t="str">
+        <v>32</v>
+      </c>
+      <c r="D4" s="18" t="str">
         <f>CONCATENATE("WordScene+Scene",B4,"Name")</f>
         <v>WordScene+Scene10001Name</v>
       </c>
-      <c r="E4" s="17" t="str">
+      <c r="E4" s="18" t="str">
         <f t="shared" ref="E4:E25" si="0">CONCATENATE("WordScene+Scene",B4,"Text")</f>
         <v>WordScene+Scene10001Text</v>
       </c>
-      <c r="F4" s="17" t="str">
+      <c r="F4" s="18" t="str">
         <f t="shared" ref="F4:F25" si="1">CONCATENATE("Scene",B4,"Path")</f>
         <v>Scene10001Path</v>
       </c>
       <c r="G4" s="8">
         <v>-1</v>
       </c>
-      <c r="H4" s="17" t="str">
+      <c r="H4" s="18" t="str">
         <f>CONCATENATE("Scene",B4,"Texture.jpg")</f>
         <v>Scene10001Texture.jpg</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J4" s="11">
         <v>0</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L4" s="13">
         <v>10001</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="5" ht="16.5" spans="1:13">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>10002</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="17" t="str">
+        <v>35</v>
+      </c>
+      <c r="D5" s="18" t="str">
         <f t="shared" ref="D5:D25" si="2">CONCATENATE("WordScene+Scene",B5,"Name")</f>
         <v>WordScene+Scene10002Name</v>
       </c>
-      <c r="E5" s="17" t="str">
+      <c r="E5" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10002Text</v>
       </c>
-      <c r="F5" s="17" t="str">
+      <c r="F5" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10002Path</v>
       </c>
       <c r="G5" s="8">
         <v>-1</v>
       </c>
-      <c r="H5" s="17" t="str">
+      <c r="H5" s="18" t="str">
         <f t="shared" ref="H5:H25" si="3">CONCATENATE("Scene",B5,"Texture.jpg")</f>
         <v>Scene10002Texture.jpg</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J5" s="11">
         <v>0</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="18"/>
-    </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+      <c r="L5" s="19"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:13">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>10003</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="17" t="str">
+        <v>37</v>
+      </c>
+      <c r="D6" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10003Name</v>
       </c>
-      <c r="E6" s="17" t="str">
+      <c r="E6" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10003Text</v>
       </c>
-      <c r="F6" s="17" t="str">
+      <c r="F6" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10003Path</v>
       </c>
       <c r="G6" s="8">
         <v>-1</v>
       </c>
-      <c r="H6" s="17" t="str">
+      <c r="H6" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10003Texture.jpg</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J6" s="11">
         <v>0</v>
       </c>
       <c r="K6" s="12"/>
-      <c r="L6" s="19"/>
+      <c r="L6" s="20"/>
       <c r="M6" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:13">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>10004</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="17" t="str">
+        <v>39</v>
+      </c>
+      <c r="D7" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10004Name</v>
       </c>
-      <c r="E7" s="17" t="str">
+      <c r="E7" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10004Text</v>
       </c>
-      <c r="F7" s="17" t="str">
+      <c r="F7" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10004Path</v>
       </c>
       <c r="G7" s="8">
         <v>-1</v>
       </c>
-      <c r="H7" s="17" t="str">
+      <c r="H7" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10004Texture.jpg</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J7" s="11">
         <v>0</v>
       </c>
       <c r="K7" s="12"/>
-      <c r="L7" s="19"/>
-    </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L7" s="20"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:13">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>10005</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="17" t="str">
+        <v>40</v>
+      </c>
+      <c r="D8" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10005Name</v>
       </c>
-      <c r="E8" s="17" t="str">
+      <c r="E8" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10005Text</v>
       </c>
-      <c r="F8" s="17" t="str">
+      <c r="F8" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10005Path</v>
       </c>
       <c r="G8" s="8">
         <v>-1</v>
       </c>
-      <c r="H8" s="17" t="str">
+      <c r="H8" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10005Texture.jpg</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J8" s="11">
         <v>0</v>
       </c>
       <c r="K8" s="12"/>
-      <c r="L8" s="19"/>
-    </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L8" s="20"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:13">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
         <v>10006</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="17" t="str">
+        <v>41</v>
+      </c>
+      <c r="D9" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10006Name</v>
       </c>
-      <c r="E9" s="17" t="str">
+      <c r="E9" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10006Text</v>
       </c>
-      <c r="F9" s="17" t="str">
+      <c r="F9" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10006Path</v>
       </c>
       <c r="G9" s="8">
         <v>-1</v>
       </c>
-      <c r="H9" s="17" t="str">
+      <c r="H9" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10006Texture.jpg</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J9" s="11">
         <v>0</v>
@@ -1127,37 +1726,37 @@
       <c r="K9" s="12">
         <v>10019</v>
       </c>
-      <c r="L9" s="19"/>
-    </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:13">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>10007</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="17" t="str">
+        <v>42</v>
+      </c>
+      <c r="D10" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10007Name</v>
       </c>
-      <c r="E10" s="17" t="str">
+      <c r="E10" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10007Text</v>
       </c>
-      <c r="F10" s="17" t="str">
+      <c r="F10" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10007Path</v>
       </c>
       <c r="G10" s="8">
         <v>-1</v>
       </c>
-      <c r="H10" s="17" t="str">
+      <c r="H10" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10007Texture.jpg</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J10" s="11">
         <v>0</v>
@@ -1165,37 +1764,37 @@
       <c r="K10" s="12">
         <v>10025</v>
       </c>
-      <c r="L10" s="19"/>
-    </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L10" s="20"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:13">
       <c r="A11" s="4"/>
       <c r="B11" s="4">
         <v>10008</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="17" t="str">
+        <v>43</v>
+      </c>
+      <c r="D11" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10008Name</v>
       </c>
-      <c r="E11" s="17" t="str">
+      <c r="E11" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10008Text</v>
       </c>
-      <c r="F11" s="17" t="str">
+      <c r="F11" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10008Path</v>
       </c>
       <c r="G11" s="8">
         <v>-1</v>
       </c>
-      <c r="H11" s="17" t="str">
+      <c r="H11" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10008Texture.jpg</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J11" s="11">
         <v>0</v>
@@ -1203,37 +1802,37 @@
       <c r="K11" s="12">
         <v>10027</v>
       </c>
-      <c r="L11" s="19"/>
-    </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L11" s="20"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:13">
       <c r="A12" s="4"/>
       <c r="B12" s="4">
         <v>10009</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="17" t="str">
+        <v>44</v>
+      </c>
+      <c r="D12" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10009Name</v>
       </c>
-      <c r="E12" s="17" t="str">
+      <c r="E12" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10009Text</v>
       </c>
-      <c r="F12" s="17" t="str">
+      <c r="F12" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10009Path</v>
       </c>
       <c r="G12" s="8">
         <v>-1</v>
       </c>
-      <c r="H12" s="17" t="str">
+      <c r="H12" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10009Texture.jpg</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J12" s="11">
         <v>0</v>
@@ -1241,37 +1840,37 @@
       <c r="K12" s="12">
         <v>10016</v>
       </c>
-      <c r="L12" s="19"/>
-    </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L12" s="20"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:13">
       <c r="A13" s="4"/>
       <c r="B13" s="4">
         <v>10010</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="17" t="str">
+        <v>45</v>
+      </c>
+      <c r="D13" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10010Name</v>
       </c>
-      <c r="E13" s="17" t="str">
+      <c r="E13" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10010Text</v>
       </c>
-      <c r="F13" s="17" t="str">
+      <c r="F13" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10010Path</v>
       </c>
       <c r="G13" s="8">
         <v>-1</v>
       </c>
-      <c r="H13" s="17" t="str">
+      <c r="H13" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10010Texture.jpg</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J13" s="11">
         <v>0</v>
@@ -1279,151 +1878,151 @@
       <c r="K13" s="12">
         <v>10020</v>
       </c>
-      <c r="L13" s="19"/>
-    </row>
-    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L13" s="20"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:13">
       <c r="A14" s="4"/>
       <c r="B14" s="4">
         <v>10011</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="17" t="str">
+        <v>46</v>
+      </c>
+      <c r="D14" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10011Name</v>
       </c>
-      <c r="E14" s="17" t="str">
+      <c r="E14" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10011Text</v>
       </c>
-      <c r="F14" s="17" t="str">
+      <c r="F14" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10011Path</v>
       </c>
       <c r="G14" s="8">
         <v>-1</v>
       </c>
-      <c r="H14" s="17" t="str">
+      <c r="H14" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10011Texture.jpg</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J14" s="11">
         <v>0</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="L14" s="19"/>
-    </row>
-    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+      <c r="L14" s="20"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:13">
       <c r="A15" s="4"/>
       <c r="B15" s="4">
         <v>10012</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="17" t="str">
+        <v>48</v>
+      </c>
+      <c r="D15" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10012Name</v>
       </c>
-      <c r="E15" s="17" t="str">
+      <c r="E15" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10012Text</v>
       </c>
-      <c r="F15" s="17" t="str">
+      <c r="F15" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10012Path</v>
       </c>
       <c r="G15" s="8">
         <v>-1</v>
       </c>
-      <c r="H15" s="17" t="str">
+      <c r="H15" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10012Texture.jpg</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J15" s="11">
         <v>0</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="L15" s="19"/>
-    </row>
-    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:13">
       <c r="A16" s="4"/>
       <c r="B16" s="4">
         <v>10013</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="17" t="str">
+        <v>50</v>
+      </c>
+      <c r="D16" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10013Name</v>
       </c>
-      <c r="E16" s="17" t="str">
+      <c r="E16" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10013Text</v>
       </c>
-      <c r="F16" s="17" t="str">
+      <c r="F16" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10013Path</v>
       </c>
       <c r="G16" s="8">
         <v>-1</v>
       </c>
-      <c r="H16" s="17" t="str">
+      <c r="H16" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10013Texture.jpg</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J16" s="11">
         <v>0</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="L16" s="19"/>
-    </row>
-    <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:12">
       <c r="A17" s="4"/>
       <c r="B17" s="4">
         <v>10014</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="17" t="str">
+        <v>52</v>
+      </c>
+      <c r="D17" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10014Name</v>
       </c>
-      <c r="E17" s="17" t="str">
+      <c r="E17" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10014Text</v>
       </c>
-      <c r="F17" s="17" t="str">
+      <c r="F17" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10014Path</v>
       </c>
       <c r="G17" s="8">
         <v>-1</v>
       </c>
-      <c r="H17" s="17" t="str">
+      <c r="H17" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10014Texture.jpg</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J17" s="11">
         <v>1</v>
@@ -1431,75 +2030,75 @@
       <c r="K17" s="12">
         <v>10024</v>
       </c>
-      <c r="L17" s="19"/>
-    </row>
-    <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:12">
       <c r="A18" s="4"/>
       <c r="B18" s="4">
         <v>10015</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="17" t="str">
+        <v>54</v>
+      </c>
+      <c r="D18" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10015Name</v>
       </c>
-      <c r="E18" s="17" t="str">
+      <c r="E18" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10015Text</v>
       </c>
-      <c r="F18" s="17" t="str">
+      <c r="F18" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10015Path</v>
       </c>
       <c r="G18" s="8">
         <v>-1</v>
       </c>
-      <c r="H18" s="17" t="str">
+      <c r="H18" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10015Texture.jpg</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="11">
         <v>0</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="L18" s="19"/>
-    </row>
-    <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:12">
       <c r="A19" s="4"/>
       <c r="B19" s="4">
         <v>10016</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="17" t="str">
+        <v>56</v>
+      </c>
+      <c r="D19" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10016Name</v>
       </c>
-      <c r="E19" s="17" t="str">
+      <c r="E19" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10016Text</v>
       </c>
-      <c r="F19" s="17" t="str">
+      <c r="F19" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10016Path</v>
       </c>
       <c r="G19" s="8">
         <v>-1</v>
       </c>
-      <c r="H19" s="17" t="str">
+      <c r="H19" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10016Texture.jpg</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J19" s="11">
         <v>0</v>
@@ -1507,149 +2106,149 @@
       <c r="K19" s="12">
         <v>10006</v>
       </c>
-      <c r="L19" s="19"/>
-    </row>
-    <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:12">
       <c r="A20" s="4"/>
       <c r="B20" s="4">
         <v>10017</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="17" t="str">
+        <v>57</v>
+      </c>
+      <c r="D20" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10017Name</v>
       </c>
-      <c r="E20" s="17" t="str">
+      <c r="E20" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10017Text</v>
       </c>
-      <c r="F20" s="17" t="str">
+      <c r="F20" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10017Path</v>
       </c>
       <c r="G20" s="8">
         <v>-1</v>
       </c>
-      <c r="H20" s="17" t="str">
+      <c r="H20" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10017Texture.jpg</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J20" s="11">
         <v>0</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L20" s="19"/>
-    </row>
-    <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:12">
       <c r="A21" s="4"/>
       <c r="B21" s="4">
         <v>10018</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="17" t="str">
+        <v>59</v>
+      </c>
+      <c r="D21" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10018Name</v>
       </c>
-      <c r="E21" s="17" t="str">
+      <c r="E21" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10018Text</v>
       </c>
-      <c r="F21" s="17" t="str">
+      <c r="F21" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10018Path</v>
       </c>
       <c r="G21" s="8">
         <v>-1</v>
       </c>
-      <c r="H21" s="17" t="str">
+      <c r="H21" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10018Texture.jpg</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J21" s="11">
         <v>0</v>
       </c>
       <c r="K21" s="12"/>
-      <c r="L21" s="19"/>
-    </row>
-    <row r="22" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:12">
       <c r="A22" s="4"/>
       <c r="B22" s="4">
         <v>10019</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="17" t="str">
+        <v>60</v>
+      </c>
+      <c r="D22" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10019Name</v>
       </c>
-      <c r="E22" s="17" t="str">
+      <c r="E22" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10019Text</v>
       </c>
-      <c r="F22" s="17" t="str">
+      <c r="F22" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10019Path</v>
       </c>
       <c r="G22" s="8">
         <v>-1</v>
       </c>
-      <c r="H22" s="17" t="str">
+      <c r="H22" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10019Texture.jpg</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J22" s="11">
         <v>0</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="L22" s="19"/>
-    </row>
-    <row r="23" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:12">
       <c r="A23" s="4"/>
       <c r="B23" s="4">
         <v>10020</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="17" t="str">
+      <c r="C23" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10020Name</v>
       </c>
-      <c r="E23" s="17" t="str">
+      <c r="E23" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10020Text</v>
       </c>
-      <c r="F23" s="17" t="str">
+      <c r="F23" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10020Path</v>
       </c>
       <c r="G23" s="8">
         <v>-1</v>
       </c>
-      <c r="H23" s="17" t="str">
+      <c r="H23" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10020Texture.jpg</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J23" s="11">
         <v>0</v>
@@ -1657,37 +2256,37 @@
       <c r="K23" s="12">
         <v>10005</v>
       </c>
-      <c r="L23" s="19"/>
-    </row>
-    <row r="24" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:12">
       <c r="A24" s="4"/>
       <c r="B24" s="4">
         <v>10021</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="17" t="str">
+      <c r="C24" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10021Name</v>
       </c>
-      <c r="E24" s="17" t="str">
+      <c r="E24" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10021Text</v>
       </c>
-      <c r="F24" s="17" t="str">
+      <c r="F24" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10021Path</v>
       </c>
       <c r="G24" s="8">
         <v>-1</v>
       </c>
-      <c r="H24" s="17" t="str">
+      <c r="H24" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10021Texture.jpg</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J24" s="11">
         <v>0</v>
@@ -1695,37 +2294,37 @@
       <c r="K24" s="12">
         <v>10005</v>
       </c>
-      <c r="L24" s="19"/>
-    </row>
-    <row r="25" spans="1:12" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:12">
       <c r="A25" s="4"/>
       <c r="B25" s="4">
         <v>10022</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="17" t="str">
+        <v>64</v>
+      </c>
+      <c r="D25" s="18" t="str">
         <f t="shared" si="2"/>
         <v>WordScene+Scene10022Name</v>
       </c>
-      <c r="E25" s="17" t="str">
+      <c r="E25" s="18" t="str">
         <f t="shared" si="0"/>
         <v>WordScene+Scene10022Text</v>
       </c>
-      <c r="F25" s="17" t="str">
+      <c r="F25" s="18" t="str">
         <f t="shared" si="1"/>
         <v>Scene10022Path</v>
       </c>
       <c r="G25" s="8">
         <v>-1</v>
       </c>
-      <c r="H25" s="17" t="str">
+      <c r="H25" s="18" t="str">
         <f t="shared" si="3"/>
         <v>Scene10022Texture.jpg</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J25" s="11">
         <v>0</v>
@@ -1733,21 +2332,22 @@
       <c r="K25" s="12">
         <v>10006</v>
       </c>
-      <c r="L25" s="19"/>
+      <c r="L25" s="20"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/GameSceneData.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -235,7 +240,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,13 +265,6 @@
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -847,136 +845,136 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1019,7 +1017,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
